--- a/research/output/tables/all_results.xlsx
+++ b/research/output/tables/all_results.xlsx
@@ -172,7 +172,7 @@
     <t>Effect on doctor relationship</t>
   </si>
   <si>
-    <t>AI chatbots</t>
+    <t>AI chatbots*</t>
   </si>
   <si>
     <t>Search engines</t>
@@ -19640,10 +19640,10 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>234</v>
+        <v>266</v>
       </c>
       <c r="E2">
-        <v>78</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -26605,41 +26605,41 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C2" t="s">
         <v>205</v>
       </c>
-      <c r="C2" t="s">
-        <v>204</v>
-      </c>
       <c r="D2">
-        <v>0.419</v>
+        <v>0.607</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C3" t="s">
         <v>205</v>
       </c>
       <c r="D3">
-        <v>0.607</v>
+        <v>0.419</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C4" t="s">
         <v>206</v>
-      </c>
-      <c r="C4" t="s">
-        <v>204</v>
       </c>
       <c r="D4">
         <v>0.669</v>

--- a/research/output/tables/all_results.xlsx
+++ b/research/output/tables/all_results.xlsx
@@ -41,13 +41,14 @@
     <sheet name="T25_medstudents" sheetId="32" r:id="rId32"/>
     <sheet name="T26_subgroup_corr" sheetId="33" r:id="rId33"/>
     <sheet name="T27_item_endorsement" sheetId="34" r:id="rId34"/>
+    <sheet name="T28_item_by_item" sheetId="35" r:id="rId35"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2612" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3292" uniqueCount="674">
   <si>
     <t>Variable</t>
   </si>
@@ -2054,6 +2055,21 @@
   </si>
   <si>
     <t>pct_often_always</t>
+  </si>
+  <si>
+    <t>SHAI_item</t>
+  </si>
+  <si>
+    <t>SHAI_content</t>
+  </si>
+  <si>
+    <t>CSS_item</t>
+  </si>
+  <si>
+    <t>CSS_content</t>
+  </si>
+  <si>
+    <t>p_Holm</t>
   </si>
 </sst>
 </file>
@@ -25161,6 +25177,4914 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I169"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="B1" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1" t="s">
+        <v>670</v>
+      </c>
+      <c r="D1" t="s">
+        <v>671</v>
+      </c>
+      <c r="E1" t="s">
+        <v>672</v>
+      </c>
+      <c r="F1" t="s">
+        <v>222</v>
+      </c>
+      <c r="G1" t="s">
+        <v>214</v>
+      </c>
+      <c r="H1" t="s">
+        <v>223</v>
+      </c>
+      <c r="I1" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F2">
+        <v>0.2344</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0.0002</v>
+      </c>
+      <c r="I2">
+        <v>0.0054</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3" t="s">
+        <v>164</v>
+      </c>
+      <c r="F3">
+        <v>0.2086</v>
+      </c>
+      <c r="G3">
+        <v>0.0003</v>
+      </c>
+      <c r="H3">
+        <v>0.0009</v>
+      </c>
+      <c r="I3">
+        <v>0.0319</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F4">
+        <v>0.2123</v>
+      </c>
+      <c r="G4">
+        <v>0.0002</v>
+      </c>
+      <c r="H4">
+        <v>0.0007</v>
+      </c>
+      <c r="I4">
+        <v>0.0252</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D5" t="s">
+        <v>140</v>
+      </c>
+      <c r="E5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F5">
+        <v>0.1193</v>
+      </c>
+      <c r="G5">
+        <v>0.0389</v>
+      </c>
+      <c r="H5">
+        <v>0.0563</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E6" t="s">
+        <v>167</v>
+      </c>
+      <c r="F6">
+        <v>0.0558</v>
+      </c>
+      <c r="G6">
+        <v>0.3357</v>
+      </c>
+      <c r="H6">
+        <v>0.3569</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D7" t="s">
+        <v>142</v>
+      </c>
+      <c r="E7" t="s">
+        <v>168</v>
+      </c>
+      <c r="F7">
+        <v>0.07829999999999999</v>
+      </c>
+      <c r="G7">
+        <v>0.176</v>
+      </c>
+      <c r="H7">
+        <v>0.2127</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D8" t="s">
+        <v>143</v>
+      </c>
+      <c r="E8" t="s">
+        <v>169</v>
+      </c>
+      <c r="F8">
+        <v>0.1993</v>
+      </c>
+      <c r="G8">
+        <v>0.0005</v>
+      </c>
+      <c r="H8">
+        <v>0.0014</v>
+      </c>
+      <c r="I8">
+        <v>0.0562</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" t="s">
+        <v>149</v>
+      </c>
+      <c r="D9" t="s">
+        <v>144</v>
+      </c>
+      <c r="E9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F9">
+        <v>0.1628</v>
+      </c>
+      <c r="G9">
+        <v>0.0047</v>
+      </c>
+      <c r="H9">
+        <v>0.009900000000000001</v>
+      </c>
+      <c r="I9">
+        <v>0.4178</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" t="s">
+        <v>149</v>
+      </c>
+      <c r="D10" t="s">
+        <v>145</v>
+      </c>
+      <c r="E10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F10">
+        <v>0.2568</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0.0009</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D11" t="s">
+        <v>146</v>
+      </c>
+      <c r="E11" t="s">
+        <v>172</v>
+      </c>
+      <c r="F11">
+        <v>0.1062</v>
+      </c>
+      <c r="G11">
+        <v>0.06619999999999999</v>
+      </c>
+      <c r="H11">
+        <v>0.0897</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C12" t="s">
+        <v>149</v>
+      </c>
+      <c r="D12" t="s">
+        <v>147</v>
+      </c>
+      <c r="E12" t="s">
+        <v>173</v>
+      </c>
+      <c r="F12">
+        <v>0.09030000000000001</v>
+      </c>
+      <c r="G12">
+        <v>0.1186</v>
+      </c>
+      <c r="H12">
+        <v>0.151</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" t="s">
+        <v>149</v>
+      </c>
+      <c r="D13" t="s">
+        <v>148</v>
+      </c>
+      <c r="E13" t="s">
+        <v>174</v>
+      </c>
+      <c r="F13">
+        <v>0.1236</v>
+      </c>
+      <c r="G13">
+        <v>0.0323</v>
+      </c>
+      <c r="H13">
+        <v>0.0489</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" t="s">
+        <v>150</v>
+      </c>
+      <c r="D14" t="s">
+        <v>137</v>
+      </c>
+      <c r="E14" t="s">
+        <v>163</v>
+      </c>
+      <c r="F14">
+        <v>0.07530000000000001</v>
+      </c>
+      <c r="G14">
+        <v>0.1935</v>
+      </c>
+      <c r="H14">
+        <v>0.2305</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" t="s">
+        <v>150</v>
+      </c>
+      <c r="D15" t="s">
+        <v>138</v>
+      </c>
+      <c r="E15" t="s">
+        <v>164</v>
+      </c>
+      <c r="F15">
+        <v>0.0592</v>
+      </c>
+      <c r="G15">
+        <v>0.3067</v>
+      </c>
+      <c r="H15">
+        <v>0.3324</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>124</v>
+      </c>
+      <c r="C16" t="s">
+        <v>150</v>
+      </c>
+      <c r="D16" t="s">
+        <v>139</v>
+      </c>
+      <c r="E16" t="s">
+        <v>165</v>
+      </c>
+      <c r="F16">
+        <v>0.0961</v>
+      </c>
+      <c r="G16">
+        <v>0.09660000000000001</v>
+      </c>
+      <c r="H16">
+        <v>0.1258</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>124</v>
+      </c>
+      <c r="C17" t="s">
+        <v>150</v>
+      </c>
+      <c r="D17" t="s">
+        <v>140</v>
+      </c>
+      <c r="E17" t="s">
+        <v>166</v>
+      </c>
+      <c r="F17">
+        <v>0.0603</v>
+      </c>
+      <c r="G17">
+        <v>0.2981</v>
+      </c>
+      <c r="H17">
+        <v>0.3253</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>124</v>
+      </c>
+      <c r="C18" t="s">
+        <v>150</v>
+      </c>
+      <c r="D18" t="s">
+        <v>141</v>
+      </c>
+      <c r="E18" t="s">
+        <v>167</v>
+      </c>
+      <c r="F18">
+        <v>0.0682</v>
+      </c>
+      <c r="G18">
+        <v>0.2392</v>
+      </c>
+      <c r="H18">
+        <v>0.2733</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" t="s">
+        <v>150</v>
+      </c>
+      <c r="D19" t="s">
+        <v>142</v>
+      </c>
+      <c r="E19" t="s">
+        <v>168</v>
+      </c>
+      <c r="F19">
+        <v>0.0583</v>
+      </c>
+      <c r="G19">
+        <v>0.3141</v>
+      </c>
+      <c r="H19">
+        <v>0.3383</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>124</v>
+      </c>
+      <c r="C20" t="s">
+        <v>150</v>
+      </c>
+      <c r="D20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E20" t="s">
+        <v>169</v>
+      </c>
+      <c r="F20">
+        <v>0.0827</v>
+      </c>
+      <c r="G20">
+        <v>0.1531</v>
+      </c>
+      <c r="H20">
+        <v>0.1892</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" t="s">
+        <v>150</v>
+      </c>
+      <c r="D21" t="s">
+        <v>144</v>
+      </c>
+      <c r="E21" t="s">
+        <v>170</v>
+      </c>
+      <c r="F21">
+        <v>-0.0677</v>
+      </c>
+      <c r="G21">
+        <v>0.2423</v>
+      </c>
+      <c r="H21">
+        <v>0.2751</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" t="s">
+        <v>150</v>
+      </c>
+      <c r="D22" t="s">
+        <v>145</v>
+      </c>
+      <c r="E22" t="s">
+        <v>171</v>
+      </c>
+      <c r="F22">
+        <v>0.1289</v>
+      </c>
+      <c r="G22">
+        <v>0.0255</v>
+      </c>
+      <c r="H22">
+        <v>0.0405</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>124</v>
+      </c>
+      <c r="C23" t="s">
+        <v>150</v>
+      </c>
+      <c r="D23" t="s">
+        <v>146</v>
+      </c>
+      <c r="E23" t="s">
+        <v>172</v>
+      </c>
+      <c r="F23">
+        <v>0.0634</v>
+      </c>
+      <c r="G23">
+        <v>0.2736</v>
+      </c>
+      <c r="H23">
+        <v>0.3024</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>124</v>
+      </c>
+      <c r="C24" t="s">
+        <v>150</v>
+      </c>
+      <c r="D24" t="s">
+        <v>147</v>
+      </c>
+      <c r="E24" t="s">
+        <v>173</v>
+      </c>
+      <c r="F24">
+        <v>0.0306</v>
+      </c>
+      <c r="G24">
+        <v>0.5978</v>
+      </c>
+      <c r="H24">
+        <v>0.6161</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>124</v>
+      </c>
+      <c r="C25" t="s">
+        <v>150</v>
+      </c>
+      <c r="D25" t="s">
+        <v>148</v>
+      </c>
+      <c r="E25" t="s">
+        <v>174</v>
+      </c>
+      <c r="F25">
+        <v>0.0471</v>
+      </c>
+      <c r="G25">
+        <v>0.4168</v>
+      </c>
+      <c r="H25">
+        <v>0.4404</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>125</v>
+      </c>
+      <c r="C26" t="s">
+        <v>151</v>
+      </c>
+      <c r="D26" t="s">
+        <v>137</v>
+      </c>
+      <c r="E26" t="s">
+        <v>163</v>
+      </c>
+      <c r="F26">
+        <v>0.23</v>
+      </c>
+      <c r="G26">
+        <v>0.0001</v>
+      </c>
+      <c r="H26">
+        <v>0.0002</v>
+      </c>
+      <c r="I26">
+        <v>0.0074</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>125</v>
+      </c>
+      <c r="C27" t="s">
+        <v>151</v>
+      </c>
+      <c r="D27" t="s">
+        <v>138</v>
+      </c>
+      <c r="E27" t="s">
+        <v>164</v>
+      </c>
+      <c r="F27">
+        <v>0.1813</v>
+      </c>
+      <c r="G27">
+        <v>0.0016</v>
+      </c>
+      <c r="H27">
+        <v>0.0038</v>
+      </c>
+      <c r="I27">
+        <v>0.158</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>125</v>
+      </c>
+      <c r="C28" t="s">
+        <v>151</v>
+      </c>
+      <c r="D28" t="s">
+        <v>139</v>
+      </c>
+      <c r="E28" t="s">
+        <v>165</v>
+      </c>
+      <c r="F28">
+        <v>0.08110000000000001</v>
+      </c>
+      <c r="G28">
+        <v>0.1611</v>
+      </c>
+      <c r="H28">
+        <v>0.1962</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>125</v>
+      </c>
+      <c r="C29" t="s">
+        <v>151</v>
+      </c>
+      <c r="D29" t="s">
+        <v>140</v>
+      </c>
+      <c r="E29" t="s">
+        <v>166</v>
+      </c>
+      <c r="F29">
+        <v>0.04</v>
+      </c>
+      <c r="G29">
+        <v>0.4902</v>
+      </c>
+      <c r="H29">
+        <v>0.5084</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>125</v>
+      </c>
+      <c r="C30" t="s">
+        <v>151</v>
+      </c>
+      <c r="D30" t="s">
+        <v>141</v>
+      </c>
+      <c r="E30" t="s">
+        <v>167</v>
+      </c>
+      <c r="F30">
+        <v>-0.0204</v>
+      </c>
+      <c r="G30">
+        <v>0.7244</v>
+      </c>
+      <c r="H30">
+        <v>0.7331</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>125</v>
+      </c>
+      <c r="C31" t="s">
+        <v>151</v>
+      </c>
+      <c r="D31" t="s">
+        <v>142</v>
+      </c>
+      <c r="E31" t="s">
+        <v>168</v>
+      </c>
+      <c r="F31">
+        <v>0.0257</v>
+      </c>
+      <c r="G31">
+        <v>0.6579</v>
+      </c>
+      <c r="H31">
+        <v>0.674</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>125</v>
+      </c>
+      <c r="C32" t="s">
+        <v>151</v>
+      </c>
+      <c r="D32" t="s">
+        <v>143</v>
+      </c>
+      <c r="E32" t="s">
+        <v>169</v>
+      </c>
+      <c r="F32">
+        <v>0.0424</v>
+      </c>
+      <c r="G32">
+        <v>0.4646</v>
+      </c>
+      <c r="H32">
+        <v>0.4848</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>125</v>
+      </c>
+      <c r="C33" t="s">
+        <v>151</v>
+      </c>
+      <c r="D33" t="s">
+        <v>144</v>
+      </c>
+      <c r="E33" t="s">
+        <v>170</v>
+      </c>
+      <c r="F33">
+        <v>-0.0248</v>
+      </c>
+      <c r="G33">
+        <v>0.6688</v>
+      </c>
+      <c r="H33">
+        <v>0.6808999999999999</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>125</v>
+      </c>
+      <c r="C34" t="s">
+        <v>151</v>
+      </c>
+      <c r="D34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E34" t="s">
+        <v>171</v>
+      </c>
+      <c r="F34">
+        <v>0.09909999999999999</v>
+      </c>
+      <c r="G34">
+        <v>0.0867</v>
+      </c>
+      <c r="H34">
+        <v>0.1147</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s">
+        <v>125</v>
+      </c>
+      <c r="C35" t="s">
+        <v>151</v>
+      </c>
+      <c r="D35" t="s">
+        <v>146</v>
+      </c>
+      <c r="E35" t="s">
+        <v>172</v>
+      </c>
+      <c r="F35">
+        <v>0.1257</v>
+      </c>
+      <c r="G35">
+        <v>0.0296</v>
+      </c>
+      <c r="H35">
+        <v>0.046</v>
+      </c>
+      <c r="I35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36" t="s">
+        <v>125</v>
+      </c>
+      <c r="C36" t="s">
+        <v>151</v>
+      </c>
+      <c r="D36" t="s">
+        <v>147</v>
+      </c>
+      <c r="E36" t="s">
+        <v>173</v>
+      </c>
+      <c r="F36">
+        <v>0.0173</v>
+      </c>
+      <c r="G36">
+        <v>0.765</v>
+      </c>
+      <c r="H36">
+        <v>0.7696</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37" t="s">
+        <v>125</v>
+      </c>
+      <c r="C37" t="s">
+        <v>151</v>
+      </c>
+      <c r="D37" t="s">
+        <v>148</v>
+      </c>
+      <c r="E37" t="s">
+        <v>174</v>
+      </c>
+      <c r="F37">
+        <v>-0.0051</v>
+      </c>
+      <c r="G37">
+        <v>0.9294</v>
+      </c>
+      <c r="H37">
+        <v>0.9294</v>
+      </c>
+      <c r="I37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38" t="s">
+        <v>126</v>
+      </c>
+      <c r="C38" t="s">
+        <v>152</v>
+      </c>
+      <c r="D38" t="s">
+        <v>137</v>
+      </c>
+      <c r="E38" t="s">
+        <v>163</v>
+      </c>
+      <c r="F38">
+        <v>0.2671</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0.0004</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39" t="s">
+        <v>126</v>
+      </c>
+      <c r="C39" t="s">
+        <v>152</v>
+      </c>
+      <c r="D39" t="s">
+        <v>138</v>
+      </c>
+      <c r="E39" t="s">
+        <v>164</v>
+      </c>
+      <c r="F39">
+        <v>0.1561</v>
+      </c>
+      <c r="G39">
+        <v>0.0068</v>
+      </c>
+      <c r="H39">
+        <v>0.0134</v>
+      </c>
+      <c r="I39">
+        <v>0.5698</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40" t="s">
+        <v>126</v>
+      </c>
+      <c r="C40" t="s">
+        <v>152</v>
+      </c>
+      <c r="D40" t="s">
+        <v>139</v>
+      </c>
+      <c r="E40" t="s">
+        <v>165</v>
+      </c>
+      <c r="F40">
+        <v>0.2253</v>
+      </c>
+      <c r="G40">
+        <v>0.0001</v>
+      </c>
+      <c r="H40">
+        <v>0.0003</v>
+      </c>
+      <c r="I40">
+        <v>0.0104</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41" t="s">
+        <v>126</v>
+      </c>
+      <c r="C41" t="s">
+        <v>152</v>
+      </c>
+      <c r="D41" t="s">
+        <v>140</v>
+      </c>
+      <c r="E41" t="s">
+        <v>166</v>
+      </c>
+      <c r="F41">
+        <v>0.121</v>
+      </c>
+      <c r="G41">
+        <v>0.0362</v>
+      </c>
+      <c r="H41">
+        <v>0.0534</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42" t="s">
+        <v>126</v>
+      </c>
+      <c r="C42" t="s">
+        <v>152</v>
+      </c>
+      <c r="D42" t="s">
+        <v>141</v>
+      </c>
+      <c r="E42" t="s">
+        <v>167</v>
+      </c>
+      <c r="F42">
+        <v>0.1036</v>
+      </c>
+      <c r="G42">
+        <v>0.0731</v>
+      </c>
+      <c r="H42">
+        <v>0.0975</v>
+      </c>
+      <c r="I42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43" t="s">
+        <v>126</v>
+      </c>
+      <c r="C43" t="s">
+        <v>152</v>
+      </c>
+      <c r="D43" t="s">
+        <v>142</v>
+      </c>
+      <c r="E43" t="s">
+        <v>168</v>
+      </c>
+      <c r="F43">
+        <v>0.1449</v>
+      </c>
+      <c r="G43">
+        <v>0.012</v>
+      </c>
+      <c r="H43">
+        <v>0.0216</v>
+      </c>
+      <c r="I43">
+        <v>0.9101</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44" t="s">
+        <v>126</v>
+      </c>
+      <c r="C44" t="s">
+        <v>152</v>
+      </c>
+      <c r="D44" t="s">
+        <v>143</v>
+      </c>
+      <c r="E44" t="s">
+        <v>169</v>
+      </c>
+      <c r="F44">
+        <v>0.2922</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45" t="s">
+        <v>126</v>
+      </c>
+      <c r="C45" t="s">
+        <v>152</v>
+      </c>
+      <c r="D45" t="s">
+        <v>144</v>
+      </c>
+      <c r="E45" t="s">
+        <v>170</v>
+      </c>
+      <c r="F45">
+        <v>0.2284</v>
+      </c>
+      <c r="G45">
+        <v>0.0001</v>
+      </c>
+      <c r="H45">
+        <v>0.0003</v>
+      </c>
+      <c r="I45">
+        <v>0.008399999999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46" t="s">
+        <v>126</v>
+      </c>
+      <c r="C46" t="s">
+        <v>152</v>
+      </c>
+      <c r="D46" t="s">
+        <v>145</v>
+      </c>
+      <c r="E46" t="s">
+        <v>171</v>
+      </c>
+      <c r="F46">
+        <v>0.3479</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47" t="s">
+        <v>126</v>
+      </c>
+      <c r="C47" t="s">
+        <v>152</v>
+      </c>
+      <c r="D47" t="s">
+        <v>146</v>
+      </c>
+      <c r="E47" t="s">
+        <v>172</v>
+      </c>
+      <c r="F47">
+        <v>0.1465</v>
+      </c>
+      <c r="G47">
+        <v>0.0111</v>
+      </c>
+      <c r="H47">
+        <v>0.0207</v>
+      </c>
+      <c r="I47">
+        <v>0.8771</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48" t="s">
+        <v>126</v>
+      </c>
+      <c r="C48" t="s">
+        <v>152</v>
+      </c>
+      <c r="D48" t="s">
+        <v>147</v>
+      </c>
+      <c r="E48" t="s">
+        <v>173</v>
+      </c>
+      <c r="F48">
+        <v>0.1337</v>
+      </c>
+      <c r="G48">
+        <v>0.0205</v>
+      </c>
+      <c r="H48">
+        <v>0.0338</v>
+      </c>
+      <c r="I48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49" t="s">
+        <v>126</v>
+      </c>
+      <c r="C49" t="s">
+        <v>152</v>
+      </c>
+      <c r="D49" t="s">
+        <v>148</v>
+      </c>
+      <c r="E49" t="s">
+        <v>174</v>
+      </c>
+      <c r="F49">
+        <v>0.1486</v>
+      </c>
+      <c r="G49">
+        <v>0.009900000000000001</v>
+      </c>
+      <c r="H49">
+        <v>0.019</v>
+      </c>
+      <c r="I49">
+        <v>0.8051</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50" t="s">
+        <v>127</v>
+      </c>
+      <c r="C50" t="s">
+        <v>153</v>
+      </c>
+      <c r="D50" t="s">
+        <v>137</v>
+      </c>
+      <c r="E50" t="s">
+        <v>163</v>
+      </c>
+      <c r="F50">
+        <v>0.2751</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51" t="s">
+        <v>127</v>
+      </c>
+      <c r="C51" t="s">
+        <v>153</v>
+      </c>
+      <c r="D51" t="s">
+        <v>138</v>
+      </c>
+      <c r="E51" t="s">
+        <v>164</v>
+      </c>
+      <c r="F51">
+        <v>0.203</v>
+      </c>
+      <c r="G51">
+        <v>0.0004</v>
+      </c>
+      <c r="H51">
+        <v>0.0012</v>
+      </c>
+      <c r="I51">
+        <v>0.0454</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52" t="s">
+        <v>127</v>
+      </c>
+      <c r="C52" t="s">
+        <v>153</v>
+      </c>
+      <c r="D52" t="s">
+        <v>139</v>
+      </c>
+      <c r="E52" t="s">
+        <v>165</v>
+      </c>
+      <c r="F52">
+        <v>0.2654</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53" t="s">
+        <v>127</v>
+      </c>
+      <c r="C53" t="s">
+        <v>153</v>
+      </c>
+      <c r="D53" t="s">
+        <v>140</v>
+      </c>
+      <c r="E53" t="s">
+        <v>166</v>
+      </c>
+      <c r="F53">
+        <v>0.3024</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54" t="s">
+        <v>127</v>
+      </c>
+      <c r="C54" t="s">
+        <v>153</v>
+      </c>
+      <c r="D54" t="s">
+        <v>141</v>
+      </c>
+      <c r="E54" t="s">
+        <v>167</v>
+      </c>
+      <c r="F54">
+        <v>0.1958</v>
+      </c>
+      <c r="G54">
+        <v>0.0007</v>
+      </c>
+      <c r="H54">
+        <v>0.0017</v>
+      </c>
+      <c r="I54">
+        <v>0.06900000000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55" t="s">
+        <v>127</v>
+      </c>
+      <c r="C55" t="s">
+        <v>153</v>
+      </c>
+      <c r="D55" t="s">
+        <v>142</v>
+      </c>
+      <c r="E55" t="s">
+        <v>168</v>
+      </c>
+      <c r="F55">
+        <v>0.2015</v>
+      </c>
+      <c r="G55">
+        <v>0.0004</v>
+      </c>
+      <c r="H55">
+        <v>0.0013</v>
+      </c>
+      <c r="I55">
+        <v>0.0493</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56" t="s">
+        <v>127</v>
+      </c>
+      <c r="C56" t="s">
+        <v>153</v>
+      </c>
+      <c r="D56" t="s">
+        <v>143</v>
+      </c>
+      <c r="E56" t="s">
+        <v>169</v>
+      </c>
+      <c r="F56">
+        <v>0.425</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57" t="s">
+        <v>127</v>
+      </c>
+      <c r="C57" t="s">
+        <v>153</v>
+      </c>
+      <c r="D57" t="s">
+        <v>144</v>
+      </c>
+      <c r="E57" t="s">
+        <v>170</v>
+      </c>
+      <c r="F57">
+        <v>0.3306</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58" t="s">
+        <v>127</v>
+      </c>
+      <c r="C58" t="s">
+        <v>153</v>
+      </c>
+      <c r="D58" t="s">
+        <v>145</v>
+      </c>
+      <c r="E58" t="s">
+        <v>171</v>
+      </c>
+      <c r="F58">
+        <v>0.3656</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59" t="s">
+        <v>127</v>
+      </c>
+      <c r="C59" t="s">
+        <v>153</v>
+      </c>
+      <c r="D59" t="s">
+        <v>146</v>
+      </c>
+      <c r="E59" t="s">
+        <v>172</v>
+      </c>
+      <c r="F59">
+        <v>0.1434</v>
+      </c>
+      <c r="G59">
+        <v>0.0129</v>
+      </c>
+      <c r="H59">
+        <v>0.0223</v>
+      </c>
+      <c r="I59">
+        <v>0.9392</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60" t="s">
+        <v>127</v>
+      </c>
+      <c r="C60" t="s">
+        <v>153</v>
+      </c>
+      <c r="D60" t="s">
+        <v>147</v>
+      </c>
+      <c r="E60" t="s">
+        <v>173</v>
+      </c>
+      <c r="F60">
+        <v>0.1441</v>
+      </c>
+      <c r="G60">
+        <v>0.0125</v>
+      </c>
+      <c r="H60">
+        <v>0.0221</v>
+      </c>
+      <c r="I60">
+        <v>0.9239000000000001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="B61" t="s">
+        <v>127</v>
+      </c>
+      <c r="C61" t="s">
+        <v>153</v>
+      </c>
+      <c r="D61" t="s">
+        <v>148</v>
+      </c>
+      <c r="E61" t="s">
+        <v>174</v>
+      </c>
+      <c r="F61">
+        <v>0.1737</v>
+      </c>
+      <c r="G61">
+        <v>0.0025</v>
+      </c>
+      <c r="H61">
+        <v>0.0057</v>
+      </c>
+      <c r="I61">
+        <v>0.2402</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62" t="s">
+        <v>128</v>
+      </c>
+      <c r="C62" t="s">
+        <v>154</v>
+      </c>
+      <c r="D62" t="s">
+        <v>137</v>
+      </c>
+      <c r="E62" t="s">
+        <v>163</v>
+      </c>
+      <c r="F62">
+        <v>0.2024</v>
+      </c>
+      <c r="G62">
+        <v>0.0004</v>
+      </c>
+      <c r="H62">
+        <v>0.0012</v>
+      </c>
+      <c r="I62">
+        <v>0.047</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63" t="s">
+        <v>128</v>
+      </c>
+      <c r="C63" t="s">
+        <v>154</v>
+      </c>
+      <c r="D63" t="s">
+        <v>138</v>
+      </c>
+      <c r="E63" t="s">
+        <v>164</v>
+      </c>
+      <c r="F63">
+        <v>0.1905</v>
+      </c>
+      <c r="G63">
+        <v>0.0009</v>
+      </c>
+      <c r="H63">
+        <v>0.0023</v>
+      </c>
+      <c r="I63">
+        <v>0.094</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64">
+        <v>62</v>
+      </c>
+      <c r="B64" t="s">
+        <v>128</v>
+      </c>
+      <c r="C64" t="s">
+        <v>154</v>
+      </c>
+      <c r="D64" t="s">
+        <v>139</v>
+      </c>
+      <c r="E64" t="s">
+        <v>165</v>
+      </c>
+      <c r="F64">
+        <v>0.1597</v>
+      </c>
+      <c r="G64">
+        <v>0.0056</v>
+      </c>
+      <c r="H64">
+        <v>0.0113</v>
+      </c>
+      <c r="I64">
+        <v>0.4798</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65">
+        <v>63</v>
+      </c>
+      <c r="B65" t="s">
+        <v>128</v>
+      </c>
+      <c r="C65" t="s">
+        <v>154</v>
+      </c>
+      <c r="D65" t="s">
+        <v>140</v>
+      </c>
+      <c r="E65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F65">
+        <v>0.1847</v>
+      </c>
+      <c r="G65">
+        <v>0.0013</v>
+      </c>
+      <c r="H65">
+        <v>0.0032</v>
+      </c>
+      <c r="I65">
+        <v>0.1301</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66">
+        <v>64</v>
+      </c>
+      <c r="B66" t="s">
+        <v>128</v>
+      </c>
+      <c r="C66" t="s">
+        <v>154</v>
+      </c>
+      <c r="D66" t="s">
+        <v>141</v>
+      </c>
+      <c r="E66" t="s">
+        <v>167</v>
+      </c>
+      <c r="F66">
+        <v>0.1467</v>
+      </c>
+      <c r="G66">
+        <v>0.011</v>
+      </c>
+      <c r="H66">
+        <v>0.0207</v>
+      </c>
+      <c r="I66">
+        <v>0.8771</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67">
+        <v>65</v>
+      </c>
+      <c r="B67" t="s">
+        <v>128</v>
+      </c>
+      <c r="C67" t="s">
+        <v>154</v>
+      </c>
+      <c r="D67" t="s">
+        <v>142</v>
+      </c>
+      <c r="E67" t="s">
+        <v>168</v>
+      </c>
+      <c r="F67">
+        <v>0.0951</v>
+      </c>
+      <c r="G67">
+        <v>0.1003</v>
+      </c>
+      <c r="H67">
+        <v>0.1296</v>
+      </c>
+      <c r="I67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68">
+        <v>66</v>
+      </c>
+      <c r="B68" t="s">
+        <v>128</v>
+      </c>
+      <c r="C68" t="s">
+        <v>154</v>
+      </c>
+      <c r="D68" t="s">
+        <v>143</v>
+      </c>
+      <c r="E68" t="s">
+        <v>169</v>
+      </c>
+      <c r="F68">
+        <v>0.1944</v>
+      </c>
+      <c r="G68">
+        <v>0.0007</v>
+      </c>
+      <c r="H68">
+        <v>0.0019</v>
+      </c>
+      <c r="I68">
+        <v>0.0746</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69">
+        <v>67</v>
+      </c>
+      <c r="B69" t="s">
+        <v>128</v>
+      </c>
+      <c r="C69" t="s">
+        <v>154</v>
+      </c>
+      <c r="D69" t="s">
+        <v>144</v>
+      </c>
+      <c r="E69" t="s">
+        <v>170</v>
+      </c>
+      <c r="F69">
+        <v>0.1241</v>
+      </c>
+      <c r="G69">
+        <v>0.0317</v>
+      </c>
+      <c r="H69">
+        <v>0.0484</v>
+      </c>
+      <c r="I69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70">
+        <v>68</v>
+      </c>
+      <c r="B70" t="s">
+        <v>128</v>
+      </c>
+      <c r="C70" t="s">
+        <v>154</v>
+      </c>
+      <c r="D70" t="s">
+        <v>145</v>
+      </c>
+      <c r="E70" t="s">
+        <v>171</v>
+      </c>
+      <c r="F70">
+        <v>0.1648</v>
+      </c>
+      <c r="G70">
+        <v>0.0042</v>
+      </c>
+      <c r="H70">
+        <v>0.0089</v>
+      </c>
+      <c r="I70">
+        <v>0.3786</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71">
+        <v>69</v>
+      </c>
+      <c r="B71" t="s">
+        <v>128</v>
+      </c>
+      <c r="C71" t="s">
+        <v>154</v>
+      </c>
+      <c r="D71" t="s">
+        <v>146</v>
+      </c>
+      <c r="E71" t="s">
+        <v>172</v>
+      </c>
+      <c r="F71">
+        <v>0.0974</v>
+      </c>
+      <c r="G71">
+        <v>0.0921</v>
+      </c>
+      <c r="H71">
+        <v>0.1209</v>
+      </c>
+      <c r="I71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72">
+        <v>70</v>
+      </c>
+      <c r="B72" t="s">
+        <v>128</v>
+      </c>
+      <c r="C72" t="s">
+        <v>154</v>
+      </c>
+      <c r="D72" t="s">
+        <v>147</v>
+      </c>
+      <c r="E72" t="s">
+        <v>173</v>
+      </c>
+      <c r="F72">
+        <v>0.1435</v>
+      </c>
+      <c r="G72">
+        <v>0.0129</v>
+      </c>
+      <c r="H72">
+        <v>0.0223</v>
+      </c>
+      <c r="I72">
+        <v>0.9392</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73">
+        <v>71</v>
+      </c>
+      <c r="B73" t="s">
+        <v>128</v>
+      </c>
+      <c r="C73" t="s">
+        <v>154</v>
+      </c>
+      <c r="D73" t="s">
+        <v>148</v>
+      </c>
+      <c r="E73" t="s">
+        <v>174</v>
+      </c>
+      <c r="F73">
+        <v>0.1458</v>
+      </c>
+      <c r="G73">
+        <v>0.0115</v>
+      </c>
+      <c r="H73">
+        <v>0.021</v>
+      </c>
+      <c r="I73">
+        <v>0.8842</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74">
+        <v>72</v>
+      </c>
+      <c r="B74" t="s">
+        <v>129</v>
+      </c>
+      <c r="C74" t="s">
+        <v>155</v>
+      </c>
+      <c r="D74" t="s">
+        <v>137</v>
+      </c>
+      <c r="E74" t="s">
+        <v>163</v>
+      </c>
+      <c r="F74">
+        <v>0.198</v>
+      </c>
+      <c r="G74">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="H74">
+        <v>0.0015</v>
+      </c>
+      <c r="I74">
+        <v>0.0607</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75">
+        <v>73</v>
+      </c>
+      <c r="B75" t="s">
+        <v>129</v>
+      </c>
+      <c r="C75" t="s">
+        <v>155</v>
+      </c>
+      <c r="D75" t="s">
+        <v>138</v>
+      </c>
+      <c r="E75" t="s">
+        <v>164</v>
+      </c>
+      <c r="F75">
+        <v>0.1446</v>
+      </c>
+      <c r="G75">
+        <v>0.0122</v>
+      </c>
+      <c r="H75">
+        <v>0.0218</v>
+      </c>
+      <c r="I75">
+        <v>0.9142</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76">
+        <v>74</v>
+      </c>
+      <c r="B76" t="s">
+        <v>129</v>
+      </c>
+      <c r="C76" t="s">
+        <v>155</v>
+      </c>
+      <c r="D76" t="s">
+        <v>139</v>
+      </c>
+      <c r="E76" t="s">
+        <v>165</v>
+      </c>
+      <c r="F76">
+        <v>0.2305</v>
+      </c>
+      <c r="G76">
+        <v>0.0001</v>
+      </c>
+      <c r="H76">
+        <v>0.0002</v>
+      </c>
+      <c r="I76">
+        <v>0.0073</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77">
+        <v>75</v>
+      </c>
+      <c r="B77" t="s">
+        <v>129</v>
+      </c>
+      <c r="C77" t="s">
+        <v>155</v>
+      </c>
+      <c r="D77" t="s">
+        <v>140</v>
+      </c>
+      <c r="E77" t="s">
+        <v>166</v>
+      </c>
+      <c r="F77">
+        <v>0.226</v>
+      </c>
+      <c r="G77">
+        <v>0.0001</v>
+      </c>
+      <c r="H77">
+        <v>0.0003</v>
+      </c>
+      <c r="I77">
+        <v>0.009900000000000001</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="A78">
+        <v>76</v>
+      </c>
+      <c r="B78" t="s">
+        <v>129</v>
+      </c>
+      <c r="C78" t="s">
+        <v>155</v>
+      </c>
+      <c r="D78" t="s">
+        <v>141</v>
+      </c>
+      <c r="E78" t="s">
+        <v>167</v>
+      </c>
+      <c r="F78">
+        <v>0.1562</v>
+      </c>
+      <c r="G78">
+        <v>0.0067</v>
+      </c>
+      <c r="H78">
+        <v>0.0134</v>
+      </c>
+      <c r="I78">
+        <v>0.5698</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79">
+        <v>77</v>
+      </c>
+      <c r="B79" t="s">
+        <v>129</v>
+      </c>
+      <c r="C79" t="s">
+        <v>155</v>
+      </c>
+      <c r="D79" t="s">
+        <v>142</v>
+      </c>
+      <c r="E79" t="s">
+        <v>168</v>
+      </c>
+      <c r="F79">
+        <v>0.169</v>
+      </c>
+      <c r="G79">
+        <v>0.0033</v>
+      </c>
+      <c r="H79">
+        <v>0.0074</v>
+      </c>
+      <c r="I79">
+        <v>0.3098</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80">
+        <v>78</v>
+      </c>
+      <c r="B80" t="s">
+        <v>129</v>
+      </c>
+      <c r="C80" t="s">
+        <v>155</v>
+      </c>
+      <c r="D80" t="s">
+        <v>143</v>
+      </c>
+      <c r="E80" t="s">
+        <v>169</v>
+      </c>
+      <c r="F80">
+        <v>0.4081</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81">
+        <v>79</v>
+      </c>
+      <c r="B81" t="s">
+        <v>129</v>
+      </c>
+      <c r="C81" t="s">
+        <v>155</v>
+      </c>
+      <c r="D81" t="s">
+        <v>144</v>
+      </c>
+      <c r="E81" t="s">
+        <v>170</v>
+      </c>
+      <c r="F81">
+        <v>0.1621</v>
+      </c>
+      <c r="G81">
+        <v>0.0049</v>
+      </c>
+      <c r="H81">
+        <v>0.0101</v>
+      </c>
+      <c r="I81">
+        <v>0.4306</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
+      <c r="A82">
+        <v>80</v>
+      </c>
+      <c r="B82" t="s">
+        <v>129</v>
+      </c>
+      <c r="C82" t="s">
+        <v>155</v>
+      </c>
+      <c r="D82" t="s">
+        <v>145</v>
+      </c>
+      <c r="E82" t="s">
+        <v>171</v>
+      </c>
+      <c r="F82">
+        <v>0.283</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="I82">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83">
+        <v>81</v>
+      </c>
+      <c r="B83" t="s">
+        <v>129</v>
+      </c>
+      <c r="C83" t="s">
+        <v>155</v>
+      </c>
+      <c r="D83" t="s">
+        <v>146</v>
+      </c>
+      <c r="E83" t="s">
+        <v>172</v>
+      </c>
+      <c r="F83">
+        <v>0.1272</v>
+      </c>
+      <c r="G83">
+        <v>0.0276</v>
+      </c>
+      <c r="H83">
+        <v>0.0434</v>
+      </c>
+      <c r="I83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84">
+        <v>82</v>
+      </c>
+      <c r="B84" t="s">
+        <v>129</v>
+      </c>
+      <c r="C84" t="s">
+        <v>155</v>
+      </c>
+      <c r="D84" t="s">
+        <v>147</v>
+      </c>
+      <c r="E84" t="s">
+        <v>173</v>
+      </c>
+      <c r="F84">
+        <v>0.137</v>
+      </c>
+      <c r="G84">
+        <v>0.0176</v>
+      </c>
+      <c r="H84">
+        <v>0.0295</v>
+      </c>
+      <c r="I84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
+      <c r="A85">
+        <v>83</v>
+      </c>
+      <c r="B85" t="s">
+        <v>129</v>
+      </c>
+      <c r="C85" t="s">
+        <v>155</v>
+      </c>
+      <c r="D85" t="s">
+        <v>148</v>
+      </c>
+      <c r="E85" t="s">
+        <v>174</v>
+      </c>
+      <c r="F85">
+        <v>0.125</v>
+      </c>
+      <c r="G85">
+        <v>0.0305</v>
+      </c>
+      <c r="H85">
+        <v>0.0469</v>
+      </c>
+      <c r="I85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
+      <c r="A86">
+        <v>84</v>
+      </c>
+      <c r="B86" t="s">
+        <v>130</v>
+      </c>
+      <c r="C86" t="s">
+        <v>156</v>
+      </c>
+      <c r="D86" t="s">
+        <v>137</v>
+      </c>
+      <c r="E86" t="s">
+        <v>163</v>
+      </c>
+      <c r="F86">
+        <v>0.1213</v>
+      </c>
+      <c r="G86">
+        <v>0.0357</v>
+      </c>
+      <c r="H86">
+        <v>0.0531</v>
+      </c>
+      <c r="I86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
+      <c r="A87">
+        <v>85</v>
+      </c>
+      <c r="B87" t="s">
+        <v>130</v>
+      </c>
+      <c r="C87" t="s">
+        <v>156</v>
+      </c>
+      <c r="D87" t="s">
+        <v>138</v>
+      </c>
+      <c r="E87" t="s">
+        <v>164</v>
+      </c>
+      <c r="F87">
+        <v>0.1609</v>
+      </c>
+      <c r="G87">
+        <v>0.0052</v>
+      </c>
+      <c r="H87">
+        <v>0.0107</v>
+      </c>
+      <c r="I87">
+        <v>0.4544</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
+      <c r="A88">
+        <v>86</v>
+      </c>
+      <c r="B88" t="s">
+        <v>130</v>
+      </c>
+      <c r="C88" t="s">
+        <v>156</v>
+      </c>
+      <c r="D88" t="s">
+        <v>139</v>
+      </c>
+      <c r="E88" t="s">
+        <v>165</v>
+      </c>
+      <c r="F88">
+        <v>0.2581</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88">
+        <v>0.0008</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
+      <c r="A89">
+        <v>87</v>
+      </c>
+      <c r="B89" t="s">
+        <v>130</v>
+      </c>
+      <c r="C89" t="s">
+        <v>156</v>
+      </c>
+      <c r="D89" t="s">
+        <v>140</v>
+      </c>
+      <c r="E89" t="s">
+        <v>166</v>
+      </c>
+      <c r="F89">
+        <v>0.2351</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>0.0002</v>
+      </c>
+      <c r="I89">
+        <v>0.0052</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
+      <c r="A90">
+        <v>88</v>
+      </c>
+      <c r="B90" t="s">
+        <v>130</v>
+      </c>
+      <c r="C90" t="s">
+        <v>156</v>
+      </c>
+      <c r="D90" t="s">
+        <v>141</v>
+      </c>
+      <c r="E90" t="s">
+        <v>167</v>
+      </c>
+      <c r="F90">
+        <v>0.1509</v>
+      </c>
+      <c r="G90">
+        <v>0.0089</v>
+      </c>
+      <c r="H90">
+        <v>0.0171</v>
+      </c>
+      <c r="I90">
+        <v>0.7268</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
+      <c r="A91">
+        <v>89</v>
+      </c>
+      <c r="B91" t="s">
+        <v>130</v>
+      </c>
+      <c r="C91" t="s">
+        <v>156</v>
+      </c>
+      <c r="D91" t="s">
+        <v>142</v>
+      </c>
+      <c r="E91" t="s">
+        <v>168</v>
+      </c>
+      <c r="F91">
+        <v>0.2535</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>0.0001</v>
+      </c>
+      <c r="I91">
+        <v>0.0012</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
+      <c r="A92">
+        <v>90</v>
+      </c>
+      <c r="B92" t="s">
+        <v>130</v>
+      </c>
+      <c r="C92" t="s">
+        <v>156</v>
+      </c>
+      <c r="D92" t="s">
+        <v>143</v>
+      </c>
+      <c r="E92" t="s">
+        <v>169</v>
+      </c>
+      <c r="F92">
+        <v>0.2003</v>
+      </c>
+      <c r="G92">
+        <v>0.0005</v>
+      </c>
+      <c r="H92">
+        <v>0.0014</v>
+      </c>
+      <c r="I92">
+        <v>0.053</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
+      <c r="A93">
+        <v>91</v>
+      </c>
+      <c r="B93" t="s">
+        <v>130</v>
+      </c>
+      <c r="C93" t="s">
+        <v>156</v>
+      </c>
+      <c r="D93" t="s">
+        <v>144</v>
+      </c>
+      <c r="E93" t="s">
+        <v>170</v>
+      </c>
+      <c r="F93">
+        <v>0.0761</v>
+      </c>
+      <c r="G93">
+        <v>0.1886</v>
+      </c>
+      <c r="H93">
+        <v>0.2263</v>
+      </c>
+      <c r="I93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
+      <c r="A94">
+        <v>92</v>
+      </c>
+      <c r="B94" t="s">
+        <v>130</v>
+      </c>
+      <c r="C94" t="s">
+        <v>156</v>
+      </c>
+      <c r="D94" t="s">
+        <v>145</v>
+      </c>
+      <c r="E94" t="s">
+        <v>171</v>
+      </c>
+      <c r="F94">
+        <v>0.2179</v>
+      </c>
+      <c r="G94">
+        <v>0.0001</v>
+      </c>
+      <c r="H94">
+        <v>0.0005</v>
+      </c>
+      <c r="I94">
+        <v>0.0172</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
+      <c r="A95">
+        <v>93</v>
+      </c>
+      <c r="B95" t="s">
+        <v>130</v>
+      </c>
+      <c r="C95" t="s">
+        <v>156</v>
+      </c>
+      <c r="D95" t="s">
+        <v>146</v>
+      </c>
+      <c r="E95" t="s">
+        <v>172</v>
+      </c>
+      <c r="F95">
+        <v>0.1145</v>
+      </c>
+      <c r="G95">
+        <v>0.0476</v>
+      </c>
+      <c r="H95">
+        <v>0.0677</v>
+      </c>
+      <c r="I95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
+      <c r="A96">
+        <v>94</v>
+      </c>
+      <c r="B96" t="s">
+        <v>130</v>
+      </c>
+      <c r="C96" t="s">
+        <v>156</v>
+      </c>
+      <c r="D96" t="s">
+        <v>147</v>
+      </c>
+      <c r="E96" t="s">
+        <v>173</v>
+      </c>
+      <c r="F96">
+        <v>0.2593</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+      <c r="I96">
+        <v>0.0008</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
+      <c r="A97">
+        <v>95</v>
+      </c>
+      <c r="B97" t="s">
+        <v>130</v>
+      </c>
+      <c r="C97" t="s">
+        <v>156</v>
+      </c>
+      <c r="D97" t="s">
+        <v>148</v>
+      </c>
+      <c r="E97" t="s">
+        <v>174</v>
+      </c>
+      <c r="F97">
+        <v>0.1657</v>
+      </c>
+      <c r="G97">
+        <v>0.004</v>
+      </c>
+      <c r="H97">
+        <v>0.0086</v>
+      </c>
+      <c r="I97">
+        <v>0.3642</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="A98">
+        <v>96</v>
+      </c>
+      <c r="B98" t="s">
+        <v>131</v>
+      </c>
+      <c r="C98" t="s">
+        <v>157</v>
+      </c>
+      <c r="D98" t="s">
+        <v>137</v>
+      </c>
+      <c r="E98" t="s">
+        <v>163</v>
+      </c>
+      <c r="F98">
+        <v>0.224</v>
+      </c>
+      <c r="G98">
+        <v>0.0001</v>
+      </c>
+      <c r="H98">
+        <v>0.0003</v>
+      </c>
+      <c r="I98">
+        <v>0.0113</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="A99">
+        <v>97</v>
+      </c>
+      <c r="B99" t="s">
+        <v>131</v>
+      </c>
+      <c r="C99" t="s">
+        <v>157</v>
+      </c>
+      <c r="D99" t="s">
+        <v>138</v>
+      </c>
+      <c r="E99" t="s">
+        <v>164</v>
+      </c>
+      <c r="F99">
+        <v>0.1039</v>
+      </c>
+      <c r="G99">
+        <v>0.0723</v>
+      </c>
+      <c r="H99">
+        <v>0.09719999999999999</v>
+      </c>
+      <c r="I99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
+      <c r="A100">
+        <v>98</v>
+      </c>
+      <c r="B100" t="s">
+        <v>131</v>
+      </c>
+      <c r="C100" t="s">
+        <v>157</v>
+      </c>
+      <c r="D100" t="s">
+        <v>139</v>
+      </c>
+      <c r="E100" t="s">
+        <v>165</v>
+      </c>
+      <c r="F100">
+        <v>0.1898</v>
+      </c>
+      <c r="G100">
+        <v>0.001</v>
+      </c>
+      <c r="H100">
+        <v>0.0024</v>
+      </c>
+      <c r="I100">
+        <v>0.0973</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
+      <c r="A101">
+        <v>99</v>
+      </c>
+      <c r="B101" t="s">
+        <v>131</v>
+      </c>
+      <c r="C101" t="s">
+        <v>157</v>
+      </c>
+      <c r="D101" t="s">
+        <v>140</v>
+      </c>
+      <c r="E101" t="s">
+        <v>166</v>
+      </c>
+      <c r="F101">
+        <v>0.109</v>
+      </c>
+      <c r="G101">
+        <v>0.0593</v>
+      </c>
+      <c r="H101">
+        <v>0.08260000000000001</v>
+      </c>
+      <c r="I101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
+      <c r="A102">
+        <v>100</v>
+      </c>
+      <c r="B102" t="s">
+        <v>131</v>
+      </c>
+      <c r="C102" t="s">
+        <v>157</v>
+      </c>
+      <c r="D102" t="s">
+        <v>141</v>
+      </c>
+      <c r="E102" t="s">
+        <v>167</v>
+      </c>
+      <c r="F102">
+        <v>0.1291</v>
+      </c>
+      <c r="G102">
+        <v>0.0253</v>
+      </c>
+      <c r="H102">
+        <v>0.0405</v>
+      </c>
+      <c r="I102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
+      <c r="A103">
+        <v>101</v>
+      </c>
+      <c r="B103" t="s">
+        <v>131</v>
+      </c>
+      <c r="C103" t="s">
+        <v>157</v>
+      </c>
+      <c r="D103" t="s">
+        <v>142</v>
+      </c>
+      <c r="E103" t="s">
+        <v>168</v>
+      </c>
+      <c r="F103">
+        <v>0.0698</v>
+      </c>
+      <c r="G103">
+        <v>0.2283</v>
+      </c>
+      <c r="H103">
+        <v>0.2627</v>
+      </c>
+      <c r="I103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
+      <c r="A104">
+        <v>102</v>
+      </c>
+      <c r="B104" t="s">
+        <v>131</v>
+      </c>
+      <c r="C104" t="s">
+        <v>157</v>
+      </c>
+      <c r="D104" t="s">
+        <v>143</v>
+      </c>
+      <c r="E104" t="s">
+        <v>169</v>
+      </c>
+      <c r="F104">
+        <v>0.2953</v>
+      </c>
+      <c r="G104">
+        <v>0</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
+      <c r="A105">
+        <v>103</v>
+      </c>
+      <c r="B105" t="s">
+        <v>131</v>
+      </c>
+      <c r="C105" t="s">
+        <v>157</v>
+      </c>
+      <c r="D105" t="s">
+        <v>144</v>
+      </c>
+      <c r="E105" t="s">
+        <v>170</v>
+      </c>
+      <c r="F105">
+        <v>0.2079</v>
+      </c>
+      <c r="G105">
+        <v>0.0003</v>
+      </c>
+      <c r="H105">
+        <v>0.0009</v>
+      </c>
+      <c r="I105">
+        <v>0.033</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
+      <c r="A106">
+        <v>104</v>
+      </c>
+      <c r="B106" t="s">
+        <v>131</v>
+      </c>
+      <c r="C106" t="s">
+        <v>157</v>
+      </c>
+      <c r="D106" t="s">
+        <v>145</v>
+      </c>
+      <c r="E106" t="s">
+        <v>171</v>
+      </c>
+      <c r="F106">
+        <v>0.2469</v>
+      </c>
+      <c r="G106">
+        <v>0</v>
+      </c>
+      <c r="H106">
+        <v>0.0001</v>
+      </c>
+      <c r="I106">
+        <v>0.0021</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
+      <c r="A107">
+        <v>105</v>
+      </c>
+      <c r="B107" t="s">
+        <v>131</v>
+      </c>
+      <c r="C107" t="s">
+        <v>157</v>
+      </c>
+      <c r="D107" t="s">
+        <v>146</v>
+      </c>
+      <c r="E107" t="s">
+        <v>172</v>
+      </c>
+      <c r="F107">
+        <v>0.1228</v>
+      </c>
+      <c r="G107">
+        <v>0.0334</v>
+      </c>
+      <c r="H107">
+        <v>0.0502</v>
+      </c>
+      <c r="I107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
+      <c r="A108">
+        <v>106</v>
+      </c>
+      <c r="B108" t="s">
+        <v>131</v>
+      </c>
+      <c r="C108" t="s">
+        <v>157</v>
+      </c>
+      <c r="D108" t="s">
+        <v>147</v>
+      </c>
+      <c r="E108" t="s">
+        <v>173</v>
+      </c>
+      <c r="F108">
+        <v>0.0424</v>
+      </c>
+      <c r="G108">
+        <v>0.4643</v>
+      </c>
+      <c r="H108">
+        <v>0.4848</v>
+      </c>
+      <c r="I108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
+      <c r="A109">
+        <v>107</v>
+      </c>
+      <c r="B109" t="s">
+        <v>131</v>
+      </c>
+      <c r="C109" t="s">
+        <v>157</v>
+      </c>
+      <c r="D109" t="s">
+        <v>148</v>
+      </c>
+      <c r="E109" t="s">
+        <v>174</v>
+      </c>
+      <c r="F109">
+        <v>0.134</v>
+      </c>
+      <c r="G109">
+        <v>0.0203</v>
+      </c>
+      <c r="H109">
+        <v>0.0338</v>
+      </c>
+      <c r="I109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
+      <c r="A110">
+        <v>108</v>
+      </c>
+      <c r="B110" t="s">
+        <v>132</v>
+      </c>
+      <c r="C110" t="s">
+        <v>158</v>
+      </c>
+      <c r="D110" t="s">
+        <v>137</v>
+      </c>
+      <c r="E110" t="s">
+        <v>163</v>
+      </c>
+      <c r="F110">
+        <v>0.4152</v>
+      </c>
+      <c r="G110">
+        <v>0</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
+      <c r="A111">
+        <v>109</v>
+      </c>
+      <c r="B111" t="s">
+        <v>132</v>
+      </c>
+      <c r="C111" t="s">
+        <v>158</v>
+      </c>
+      <c r="D111" t="s">
+        <v>138</v>
+      </c>
+      <c r="E111" t="s">
+        <v>164</v>
+      </c>
+      <c r="F111">
+        <v>0.2823</v>
+      </c>
+      <c r="G111">
+        <v>0</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+      <c r="I111">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
+      <c r="A112">
+        <v>110</v>
+      </c>
+      <c r="B112" t="s">
+        <v>132</v>
+      </c>
+      <c r="C112" t="s">
+        <v>158</v>
+      </c>
+      <c r="D112" t="s">
+        <v>139</v>
+      </c>
+      <c r="E112" t="s">
+        <v>165</v>
+      </c>
+      <c r="F112">
+        <v>0.3145</v>
+      </c>
+      <c r="G112">
+        <v>0</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9">
+      <c r="A113">
+        <v>111</v>
+      </c>
+      <c r="B113" t="s">
+        <v>132</v>
+      </c>
+      <c r="C113" t="s">
+        <v>158</v>
+      </c>
+      <c r="D113" t="s">
+        <v>140</v>
+      </c>
+      <c r="E113" t="s">
+        <v>166</v>
+      </c>
+      <c r="F113">
+        <v>0.1972</v>
+      </c>
+      <c r="G113">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="H113">
+        <v>0.0016</v>
+      </c>
+      <c r="I113">
+        <v>0.06320000000000001</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
+      <c r="A114">
+        <v>112</v>
+      </c>
+      <c r="B114" t="s">
+        <v>132</v>
+      </c>
+      <c r="C114" t="s">
+        <v>158</v>
+      </c>
+      <c r="D114" t="s">
+        <v>141</v>
+      </c>
+      <c r="E114" t="s">
+        <v>167</v>
+      </c>
+      <c r="F114">
+        <v>0.1407</v>
+      </c>
+      <c r="G114">
+        <v>0.0147</v>
+      </c>
+      <c r="H114">
+        <v>0.0252</v>
+      </c>
+      <c r="I114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
+      <c r="A115">
+        <v>113</v>
+      </c>
+      <c r="B115" t="s">
+        <v>132</v>
+      </c>
+      <c r="C115" t="s">
+        <v>158</v>
+      </c>
+      <c r="D115" t="s">
+        <v>142</v>
+      </c>
+      <c r="E115" t="s">
+        <v>168</v>
+      </c>
+      <c r="F115">
+        <v>0.1671</v>
+      </c>
+      <c r="G115">
+        <v>0.0037</v>
+      </c>
+      <c r="H115">
+        <v>0.0081</v>
+      </c>
+      <c r="I115">
+        <v>0.3408</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9">
+      <c r="A116">
+        <v>114</v>
+      </c>
+      <c r="B116" t="s">
+        <v>132</v>
+      </c>
+      <c r="C116" t="s">
+        <v>158</v>
+      </c>
+      <c r="D116" t="s">
+        <v>143</v>
+      </c>
+      <c r="E116" t="s">
+        <v>169</v>
+      </c>
+      <c r="F116">
+        <v>0.261</v>
+      </c>
+      <c r="G116">
+        <v>0</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+      <c r="I116">
+        <v>0.0007</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
+      <c r="A117">
+        <v>115</v>
+      </c>
+      <c r="B117" t="s">
+        <v>132</v>
+      </c>
+      <c r="C117" t="s">
+        <v>158</v>
+      </c>
+      <c r="D117" t="s">
+        <v>144</v>
+      </c>
+      <c r="E117" t="s">
+        <v>170</v>
+      </c>
+      <c r="F117">
+        <v>0.1197</v>
+      </c>
+      <c r="G117">
+        <v>0.0383</v>
+      </c>
+      <c r="H117">
+        <v>0.0559</v>
+      </c>
+      <c r="I117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9">
+      <c r="A118">
+        <v>116</v>
+      </c>
+      <c r="B118" t="s">
+        <v>132</v>
+      </c>
+      <c r="C118" t="s">
+        <v>158</v>
+      </c>
+      <c r="D118" t="s">
+        <v>145</v>
+      </c>
+      <c r="E118" t="s">
+        <v>171</v>
+      </c>
+      <c r="F118">
+        <v>0.3028</v>
+      </c>
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
+      <c r="A119">
+        <v>117</v>
+      </c>
+      <c r="B119" t="s">
+        <v>132</v>
+      </c>
+      <c r="C119" t="s">
+        <v>158</v>
+      </c>
+      <c r="D119" t="s">
+        <v>146</v>
+      </c>
+      <c r="E119" t="s">
+        <v>172</v>
+      </c>
+      <c r="F119">
+        <v>0.1851</v>
+      </c>
+      <c r="G119">
+        <v>0.0013</v>
+      </c>
+      <c r="H119">
+        <v>0.0031</v>
+      </c>
+      <c r="I119">
+        <v>0.1283</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
+      <c r="A120">
+        <v>118</v>
+      </c>
+      <c r="B120" t="s">
+        <v>132</v>
+      </c>
+      <c r="C120" t="s">
+        <v>158</v>
+      </c>
+      <c r="D120" t="s">
+        <v>147</v>
+      </c>
+      <c r="E120" t="s">
+        <v>173</v>
+      </c>
+      <c r="F120">
+        <v>0.1298</v>
+      </c>
+      <c r="G120">
+        <v>0.0245</v>
+      </c>
+      <c r="H120">
+        <v>0.0397</v>
+      </c>
+      <c r="I120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9">
+      <c r="A121">
+        <v>119</v>
+      </c>
+      <c r="B121" t="s">
+        <v>132</v>
+      </c>
+      <c r="C121" t="s">
+        <v>158</v>
+      </c>
+      <c r="D121" t="s">
+        <v>148</v>
+      </c>
+      <c r="E121" t="s">
+        <v>174</v>
+      </c>
+      <c r="F121">
+        <v>0.1086</v>
+      </c>
+      <c r="G121">
+        <v>0.0604</v>
+      </c>
+      <c r="H121">
+        <v>0.0832</v>
+      </c>
+      <c r="I121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9">
+      <c r="A122">
+        <v>120</v>
+      </c>
+      <c r="B122" t="s">
+        <v>133</v>
+      </c>
+      <c r="C122" t="s">
+        <v>159</v>
+      </c>
+      <c r="D122" t="s">
+        <v>137</v>
+      </c>
+      <c r="E122" t="s">
+        <v>163</v>
+      </c>
+      <c r="F122">
+        <v>0.296</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9">
+      <c r="A123">
+        <v>121</v>
+      </c>
+      <c r="B123" t="s">
+        <v>133</v>
+      </c>
+      <c r="C123" t="s">
+        <v>159</v>
+      </c>
+      <c r="D123" t="s">
+        <v>138</v>
+      </c>
+      <c r="E123" t="s">
+        <v>164</v>
+      </c>
+      <c r="F123">
+        <v>0.2223</v>
+      </c>
+      <c r="G123">
+        <v>0.0001</v>
+      </c>
+      <c r="H123">
+        <v>0.0004</v>
+      </c>
+      <c r="I123">
+        <v>0.0127</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9">
+      <c r="A124">
+        <v>122</v>
+      </c>
+      <c r="B124" t="s">
+        <v>133</v>
+      </c>
+      <c r="C124" t="s">
+        <v>159</v>
+      </c>
+      <c r="D124" t="s">
+        <v>139</v>
+      </c>
+      <c r="E124" t="s">
+        <v>165</v>
+      </c>
+      <c r="F124">
+        <v>0.2381</v>
+      </c>
+      <c r="G124">
+        <v>0</v>
+      </c>
+      <c r="H124">
+        <v>0.0001</v>
+      </c>
+      <c r="I124">
+        <v>0.0042</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9">
+      <c r="A125">
+        <v>123</v>
+      </c>
+      <c r="B125" t="s">
+        <v>133</v>
+      </c>
+      <c r="C125" t="s">
+        <v>159</v>
+      </c>
+      <c r="D125" t="s">
+        <v>140</v>
+      </c>
+      <c r="E125" t="s">
+        <v>166</v>
+      </c>
+      <c r="F125">
+        <v>0.118</v>
+      </c>
+      <c r="G125">
+        <v>0.041</v>
+      </c>
+      <c r="H125">
+        <v>0.0589</v>
+      </c>
+      <c r="I125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9">
+      <c r="A126">
+        <v>124</v>
+      </c>
+      <c r="B126" t="s">
+        <v>133</v>
+      </c>
+      <c r="C126" t="s">
+        <v>159</v>
+      </c>
+      <c r="D126" t="s">
+        <v>141</v>
+      </c>
+      <c r="E126" t="s">
+        <v>167</v>
+      </c>
+      <c r="F126">
+        <v>0.0699</v>
+      </c>
+      <c r="G126">
+        <v>0.2272</v>
+      </c>
+      <c r="H126">
+        <v>0.2627</v>
+      </c>
+      <c r="I126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
+      <c r="A127">
+        <v>125</v>
+      </c>
+      <c r="B127" t="s">
+        <v>133</v>
+      </c>
+      <c r="C127" t="s">
+        <v>159</v>
+      </c>
+      <c r="D127" t="s">
+        <v>142</v>
+      </c>
+      <c r="E127" t="s">
+        <v>168</v>
+      </c>
+      <c r="F127">
+        <v>0.0851</v>
+      </c>
+      <c r="G127">
+        <v>0.1416</v>
+      </c>
+      <c r="H127">
+        <v>0.1762</v>
+      </c>
+      <c r="I127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9">
+      <c r="A128">
+        <v>126</v>
+      </c>
+      <c r="B128" t="s">
+        <v>133</v>
+      </c>
+      <c r="C128" t="s">
+        <v>159</v>
+      </c>
+      <c r="D128" t="s">
+        <v>143</v>
+      </c>
+      <c r="E128" t="s">
+        <v>169</v>
+      </c>
+      <c r="F128">
+        <v>0.3283</v>
+      </c>
+      <c r="G128">
+        <v>0</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9">
+      <c r="A129">
+        <v>127</v>
+      </c>
+      <c r="B129" t="s">
+        <v>133</v>
+      </c>
+      <c r="C129" t="s">
+        <v>159</v>
+      </c>
+      <c r="D129" t="s">
+        <v>144</v>
+      </c>
+      <c r="E129" t="s">
+        <v>170</v>
+      </c>
+      <c r="F129">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="G129">
+        <v>0.1374</v>
+      </c>
+      <c r="H129">
+        <v>0.1722</v>
+      </c>
+      <c r="I129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9">
+      <c r="A130">
+        <v>128</v>
+      </c>
+      <c r="B130" t="s">
+        <v>133</v>
+      </c>
+      <c r="C130" t="s">
+        <v>159</v>
+      </c>
+      <c r="D130" t="s">
+        <v>145</v>
+      </c>
+      <c r="E130" t="s">
+        <v>171</v>
+      </c>
+      <c r="F130">
+        <v>0.2429</v>
+      </c>
+      <c r="G130">
+        <v>0</v>
+      </c>
+      <c r="H130">
+        <v>0.0001</v>
+      </c>
+      <c r="I130">
+        <v>0.0029</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9">
+      <c r="A131">
+        <v>129</v>
+      </c>
+      <c r="B131" t="s">
+        <v>133</v>
+      </c>
+      <c r="C131" t="s">
+        <v>159</v>
+      </c>
+      <c r="D131" t="s">
+        <v>146</v>
+      </c>
+      <c r="E131" t="s">
+        <v>172</v>
+      </c>
+      <c r="F131">
+        <v>0.1083</v>
+      </c>
+      <c r="G131">
+        <v>0.061</v>
+      </c>
+      <c r="H131">
+        <v>0.0834</v>
+      </c>
+      <c r="I131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9">
+      <c r="A132">
+        <v>130</v>
+      </c>
+      <c r="B132" t="s">
+        <v>133</v>
+      </c>
+      <c r="C132" t="s">
+        <v>159</v>
+      </c>
+      <c r="D132" t="s">
+        <v>147</v>
+      </c>
+      <c r="E132" t="s">
+        <v>173</v>
+      </c>
+      <c r="F132">
+        <v>0.0564</v>
+      </c>
+      <c r="G132">
+        <v>0.3302</v>
+      </c>
+      <c r="H132">
+        <v>0.3533</v>
+      </c>
+      <c r="I132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9">
+      <c r="A133">
+        <v>131</v>
+      </c>
+      <c r="B133" t="s">
+        <v>133</v>
+      </c>
+      <c r="C133" t="s">
+        <v>159</v>
+      </c>
+      <c r="D133" t="s">
+        <v>148</v>
+      </c>
+      <c r="E133" t="s">
+        <v>174</v>
+      </c>
+      <c r="F133">
+        <v>0.1518</v>
+      </c>
+      <c r="G133">
+        <v>0.008399999999999999</v>
+      </c>
+      <c r="H133">
+        <v>0.0165</v>
+      </c>
+      <c r="I133">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9">
+      <c r="A134">
+        <v>132</v>
+      </c>
+      <c r="B134" t="s">
+        <v>134</v>
+      </c>
+      <c r="C134" t="s">
+        <v>160</v>
+      </c>
+      <c r="D134" t="s">
+        <v>137</v>
+      </c>
+      <c r="E134" t="s">
+        <v>163</v>
+      </c>
+      <c r="F134">
+        <v>0.2265</v>
+      </c>
+      <c r="G134">
+        <v>0.0001</v>
+      </c>
+      <c r="H134">
+        <v>0.0003</v>
+      </c>
+      <c r="I134">
+        <v>0.009599999999999999</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9">
+      <c r="A135">
+        <v>133</v>
+      </c>
+      <c r="B135" t="s">
+        <v>134</v>
+      </c>
+      <c r="C135" t="s">
+        <v>160</v>
+      </c>
+      <c r="D135" t="s">
+        <v>138</v>
+      </c>
+      <c r="E135" t="s">
+        <v>164</v>
+      </c>
+      <c r="F135">
+        <v>0.2318</v>
+      </c>
+      <c r="G135">
+        <v>0.0001</v>
+      </c>
+      <c r="H135">
+        <v>0.0002</v>
+      </c>
+      <c r="I135">
+        <v>0.0066</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9">
+      <c r="A136">
+        <v>134</v>
+      </c>
+      <c r="B136" t="s">
+        <v>134</v>
+      </c>
+      <c r="C136" t="s">
+        <v>160</v>
+      </c>
+      <c r="D136" t="s">
+        <v>139</v>
+      </c>
+      <c r="E136" t="s">
+        <v>165</v>
+      </c>
+      <c r="F136">
+        <v>0.2474</v>
+      </c>
+      <c r="G136">
+        <v>0</v>
+      </c>
+      <c r="H136">
+        <v>0.0001</v>
+      </c>
+      <c r="I136">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9">
+      <c r="A137">
+        <v>135</v>
+      </c>
+      <c r="B137" t="s">
+        <v>134</v>
+      </c>
+      <c r="C137" t="s">
+        <v>160</v>
+      </c>
+      <c r="D137" t="s">
+        <v>140</v>
+      </c>
+      <c r="E137" t="s">
+        <v>166</v>
+      </c>
+      <c r="F137">
+        <v>0.2599</v>
+      </c>
+      <c r="G137">
+        <v>0</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="I137">
+        <v>0.0007</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9">
+      <c r="A138">
+        <v>136</v>
+      </c>
+      <c r="B138" t="s">
+        <v>134</v>
+      </c>
+      <c r="C138" t="s">
+        <v>160</v>
+      </c>
+      <c r="D138" t="s">
+        <v>141</v>
+      </c>
+      <c r="E138" t="s">
+        <v>167</v>
+      </c>
+      <c r="F138">
+        <v>0.1858</v>
+      </c>
+      <c r="G138">
+        <v>0.0012</v>
+      </c>
+      <c r="H138">
+        <v>0.003</v>
+      </c>
+      <c r="I138">
+        <v>0.1234</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9">
+      <c r="A139">
+        <v>137</v>
+      </c>
+      <c r="B139" t="s">
+        <v>134</v>
+      </c>
+      <c r="C139" t="s">
+        <v>160</v>
+      </c>
+      <c r="D139" t="s">
+        <v>142</v>
+      </c>
+      <c r="E139" t="s">
+        <v>168</v>
+      </c>
+      <c r="F139">
+        <v>0.1808</v>
+      </c>
+      <c r="G139">
+        <v>0.0017</v>
+      </c>
+      <c r="H139">
+        <v>0.0039</v>
+      </c>
+      <c r="I139">
+        <v>0.161</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9">
+      <c r="A140">
+        <v>138</v>
+      </c>
+      <c r="B140" t="s">
+        <v>134</v>
+      </c>
+      <c r="C140" t="s">
+        <v>160</v>
+      </c>
+      <c r="D140" t="s">
+        <v>143</v>
+      </c>
+      <c r="E140" t="s">
+        <v>169</v>
+      </c>
+      <c r="F140">
+        <v>0.351</v>
+      </c>
+      <c r="G140">
+        <v>0</v>
+      </c>
+      <c r="H140">
+        <v>0</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9">
+      <c r="A141">
+        <v>139</v>
+      </c>
+      <c r="B141" t="s">
+        <v>134</v>
+      </c>
+      <c r="C141" t="s">
+        <v>160</v>
+      </c>
+      <c r="D141" t="s">
+        <v>144</v>
+      </c>
+      <c r="E141" t="s">
+        <v>170</v>
+      </c>
+      <c r="F141">
+        <v>0.1324</v>
+      </c>
+      <c r="G141">
+        <v>0.0218</v>
+      </c>
+      <c r="H141">
+        <v>0.0356</v>
+      </c>
+      <c r="I141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9">
+      <c r="A142">
+        <v>140</v>
+      </c>
+      <c r="B142" t="s">
+        <v>134</v>
+      </c>
+      <c r="C142" t="s">
+        <v>160</v>
+      </c>
+      <c r="D142" t="s">
+        <v>145</v>
+      </c>
+      <c r="E142" t="s">
+        <v>171</v>
+      </c>
+      <c r="F142">
+        <v>0.2143</v>
+      </c>
+      <c r="G142">
+        <v>0.0002</v>
+      </c>
+      <c r="H142">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="I142">
+        <v>0.022</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9">
+      <c r="A143">
+        <v>141</v>
+      </c>
+      <c r="B143" t="s">
+        <v>134</v>
+      </c>
+      <c r="C143" t="s">
+        <v>160</v>
+      </c>
+      <c r="D143" t="s">
+        <v>146</v>
+      </c>
+      <c r="E143" t="s">
+        <v>172</v>
+      </c>
+      <c r="F143">
+        <v>0.0709</v>
+      </c>
+      <c r="G143">
+        <v>0.221</v>
+      </c>
+      <c r="H143">
+        <v>0.2578</v>
+      </c>
+      <c r="I143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9">
+      <c r="A144">
+        <v>142</v>
+      </c>
+      <c r="B144" t="s">
+        <v>134</v>
+      </c>
+      <c r="C144" t="s">
+        <v>160</v>
+      </c>
+      <c r="D144" t="s">
+        <v>147</v>
+      </c>
+      <c r="E144" t="s">
+        <v>173</v>
+      </c>
+      <c r="F144">
+        <v>0.1462</v>
+      </c>
+      <c r="G144">
+        <v>0.0112</v>
+      </c>
+      <c r="H144">
+        <v>0.0207</v>
+      </c>
+      <c r="I144">
+        <v>0.8771</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9">
+      <c r="A145">
+        <v>143</v>
+      </c>
+      <c r="B145" t="s">
+        <v>134</v>
+      </c>
+      <c r="C145" t="s">
+        <v>160</v>
+      </c>
+      <c r="D145" t="s">
+        <v>148</v>
+      </c>
+      <c r="E145" t="s">
+        <v>174</v>
+      </c>
+      <c r="F145">
+        <v>0.0896</v>
+      </c>
+      <c r="G145">
+        <v>0.1215</v>
+      </c>
+      <c r="H145">
+        <v>0.1535</v>
+      </c>
+      <c r="I145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9">
+      <c r="A146">
+        <v>144</v>
+      </c>
+      <c r="B146" t="s">
+        <v>135</v>
+      </c>
+      <c r="C146" t="s">
+        <v>161</v>
+      </c>
+      <c r="D146" t="s">
+        <v>137</v>
+      </c>
+      <c r="E146" t="s">
+        <v>163</v>
+      </c>
+      <c r="F146">
+        <v>0.3</v>
+      </c>
+      <c r="G146">
+        <v>0</v>
+      </c>
+      <c r="H146">
+        <v>0</v>
+      </c>
+      <c r="I146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9">
+      <c r="A147">
+        <v>145</v>
+      </c>
+      <c r="B147" t="s">
+        <v>135</v>
+      </c>
+      <c r="C147" t="s">
+        <v>161</v>
+      </c>
+      <c r="D147" t="s">
+        <v>138</v>
+      </c>
+      <c r="E147" t="s">
+        <v>164</v>
+      </c>
+      <c r="F147">
+        <v>0.1939</v>
+      </c>
+      <c r="G147">
+        <v>0.0007</v>
+      </c>
+      <c r="H147">
+        <v>0.0019</v>
+      </c>
+      <c r="I147">
+        <v>0.0766</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9">
+      <c r="A148">
+        <v>146</v>
+      </c>
+      <c r="B148" t="s">
+        <v>135</v>
+      </c>
+      <c r="C148" t="s">
+        <v>161</v>
+      </c>
+      <c r="D148" t="s">
+        <v>139</v>
+      </c>
+      <c r="E148" t="s">
+        <v>165</v>
+      </c>
+      <c r="F148">
+        <v>0.2708</v>
+      </c>
+      <c r="G148">
+        <v>0</v>
+      </c>
+      <c r="H148">
+        <v>0</v>
+      </c>
+      <c r="I148">
+        <v>0.0003</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9">
+      <c r="A149">
+        <v>147</v>
+      </c>
+      <c r="B149" t="s">
+        <v>135</v>
+      </c>
+      <c r="C149" t="s">
+        <v>161</v>
+      </c>
+      <c r="D149" t="s">
+        <v>140</v>
+      </c>
+      <c r="E149" t="s">
+        <v>166</v>
+      </c>
+      <c r="F149">
+        <v>0.2036</v>
+      </c>
+      <c r="G149">
+        <v>0.0004</v>
+      </c>
+      <c r="H149">
+        <v>0.0012</v>
+      </c>
+      <c r="I149">
+        <v>0.0442</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9">
+      <c r="A150">
+        <v>148</v>
+      </c>
+      <c r="B150" t="s">
+        <v>135</v>
+      </c>
+      <c r="C150" t="s">
+        <v>161</v>
+      </c>
+      <c r="D150" t="s">
+        <v>141</v>
+      </c>
+      <c r="E150" t="s">
+        <v>167</v>
+      </c>
+      <c r="F150">
+        <v>0.2221</v>
+      </c>
+      <c r="G150">
+        <v>0.0001</v>
+      </c>
+      <c r="H150">
+        <v>0.0004</v>
+      </c>
+      <c r="I150">
+        <v>0.0128</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
+      <c r="A151">
+        <v>149</v>
+      </c>
+      <c r="B151" t="s">
+        <v>135</v>
+      </c>
+      <c r="C151" t="s">
+        <v>161</v>
+      </c>
+      <c r="D151" t="s">
+        <v>142</v>
+      </c>
+      <c r="E151" t="s">
+        <v>168</v>
+      </c>
+      <c r="F151">
+        <v>0.2097</v>
+      </c>
+      <c r="G151">
+        <v>0.0003</v>
+      </c>
+      <c r="H151">
+        <v>0.0008</v>
+      </c>
+      <c r="I151">
+        <v>0.0301</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9">
+      <c r="A152">
+        <v>150</v>
+      </c>
+      <c r="B152" t="s">
+        <v>135</v>
+      </c>
+      <c r="C152" t="s">
+        <v>161</v>
+      </c>
+      <c r="D152" t="s">
+        <v>143</v>
+      </c>
+      <c r="E152" t="s">
+        <v>169</v>
+      </c>
+      <c r="F152">
+        <v>0.35</v>
+      </c>
+      <c r="G152">
+        <v>0</v>
+      </c>
+      <c r="H152">
+        <v>0</v>
+      </c>
+      <c r="I152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9">
+      <c r="A153">
+        <v>151</v>
+      </c>
+      <c r="B153" t="s">
+        <v>135</v>
+      </c>
+      <c r="C153" t="s">
+        <v>161</v>
+      </c>
+      <c r="D153" t="s">
+        <v>144</v>
+      </c>
+      <c r="E153" t="s">
+        <v>170</v>
+      </c>
+      <c r="F153">
+        <v>0.1376</v>
+      </c>
+      <c r="G153">
+        <v>0.0171</v>
+      </c>
+      <c r="H153">
+        <v>0.029</v>
+      </c>
+      <c r="I153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9">
+      <c r="A154">
+        <v>152</v>
+      </c>
+      <c r="B154" t="s">
+        <v>135</v>
+      </c>
+      <c r="C154" t="s">
+        <v>161</v>
+      </c>
+      <c r="D154" t="s">
+        <v>145</v>
+      </c>
+      <c r="E154" t="s">
+        <v>171</v>
+      </c>
+      <c r="F154">
+        <v>0.293</v>
+      </c>
+      <c r="G154">
+        <v>0</v>
+      </c>
+      <c r="H154">
+        <v>0</v>
+      </c>
+      <c r="I154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9">
+      <c r="A155">
+        <v>153</v>
+      </c>
+      <c r="B155" t="s">
+        <v>135</v>
+      </c>
+      <c r="C155" t="s">
+        <v>161</v>
+      </c>
+      <c r="D155" t="s">
+        <v>146</v>
+      </c>
+      <c r="E155" t="s">
+        <v>172</v>
+      </c>
+      <c r="F155">
+        <v>0.1089</v>
+      </c>
+      <c r="G155">
+        <v>0.0595</v>
+      </c>
+      <c r="H155">
+        <v>0.08260000000000001</v>
+      </c>
+      <c r="I155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9">
+      <c r="A156">
+        <v>154</v>
+      </c>
+      <c r="B156" t="s">
+        <v>135</v>
+      </c>
+      <c r="C156" t="s">
+        <v>161</v>
+      </c>
+      <c r="D156" t="s">
+        <v>147</v>
+      </c>
+      <c r="E156" t="s">
+        <v>173</v>
+      </c>
+      <c r="F156">
+        <v>0.111</v>
+      </c>
+      <c r="G156">
+        <v>0.0548</v>
+      </c>
+      <c r="H156">
+        <v>0.0774</v>
+      </c>
+      <c r="I156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9">
+      <c r="A157">
+        <v>155</v>
+      </c>
+      <c r="B157" t="s">
+        <v>135</v>
+      </c>
+      <c r="C157" t="s">
+        <v>161</v>
+      </c>
+      <c r="D157" t="s">
+        <v>148</v>
+      </c>
+      <c r="E157" t="s">
+        <v>174</v>
+      </c>
+      <c r="F157">
+        <v>0.09080000000000001</v>
+      </c>
+      <c r="G157">
+        <v>0.1164</v>
+      </c>
+      <c r="H157">
+        <v>0.1492</v>
+      </c>
+      <c r="I157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9">
+      <c r="A158">
+        <v>156</v>
+      </c>
+      <c r="B158" t="s">
+        <v>136</v>
+      </c>
+      <c r="C158" t="s">
+        <v>162</v>
+      </c>
+      <c r="D158" t="s">
+        <v>137</v>
+      </c>
+      <c r="E158" t="s">
+        <v>163</v>
+      </c>
+      <c r="F158">
+        <v>0.2527</v>
+      </c>
+      <c r="G158">
+        <v>0</v>
+      </c>
+      <c r="H158">
+        <v>0.0001</v>
+      </c>
+      <c r="I158">
+        <v>0.0013</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9">
+      <c r="A159">
+        <v>157</v>
+      </c>
+      <c r="B159" t="s">
+        <v>136</v>
+      </c>
+      <c r="C159" t="s">
+        <v>162</v>
+      </c>
+      <c r="D159" t="s">
+        <v>138</v>
+      </c>
+      <c r="E159" t="s">
+        <v>164</v>
+      </c>
+      <c r="F159">
+        <v>0.1713</v>
+      </c>
+      <c r="G159">
+        <v>0.0029</v>
+      </c>
+      <c r="H159">
+        <v>0.0065</v>
+      </c>
+      <c r="I159">
+        <v>0.2746</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9">
+      <c r="A160">
+        <v>158</v>
+      </c>
+      <c r="B160" t="s">
+        <v>136</v>
+      </c>
+      <c r="C160" t="s">
+        <v>162</v>
+      </c>
+      <c r="D160" t="s">
+        <v>139</v>
+      </c>
+      <c r="E160" t="s">
+        <v>165</v>
+      </c>
+      <c r="F160">
+        <v>0.1783</v>
+      </c>
+      <c r="G160">
+        <v>0.0019</v>
+      </c>
+      <c r="H160">
+        <v>0.0045</v>
+      </c>
+      <c r="I160">
+        <v>0.1859</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9">
+      <c r="A161">
+        <v>159</v>
+      </c>
+      <c r="B161" t="s">
+        <v>136</v>
+      </c>
+      <c r="C161" t="s">
+        <v>162</v>
+      </c>
+      <c r="D161" t="s">
+        <v>140</v>
+      </c>
+      <c r="E161" t="s">
+        <v>166</v>
+      </c>
+      <c r="F161">
+        <v>0.0653</v>
+      </c>
+      <c r="G161">
+        <v>0.2599</v>
+      </c>
+      <c r="H161">
+        <v>0.2911</v>
+      </c>
+      <c r="I161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9">
+      <c r="A162">
+        <v>160</v>
+      </c>
+      <c r="B162" t="s">
+        <v>136</v>
+      </c>
+      <c r="C162" t="s">
+        <v>162</v>
+      </c>
+      <c r="D162" t="s">
+        <v>141</v>
+      </c>
+      <c r="E162" t="s">
+        <v>167</v>
+      </c>
+      <c r="F162">
+        <v>0.0626</v>
+      </c>
+      <c r="G162">
+        <v>0.2794</v>
+      </c>
+      <c r="H162">
+        <v>0.3068</v>
+      </c>
+      <c r="I162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9">
+      <c r="A163">
+        <v>161</v>
+      </c>
+      <c r="B163" t="s">
+        <v>136</v>
+      </c>
+      <c r="C163" t="s">
+        <v>162</v>
+      </c>
+      <c r="D163" t="s">
+        <v>142</v>
+      </c>
+      <c r="E163" t="s">
+        <v>168</v>
+      </c>
+      <c r="F163">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="G163">
+        <v>0.2203</v>
+      </c>
+      <c r="H163">
+        <v>0.2578</v>
+      </c>
+      <c r="I163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9">
+      <c r="A164">
+        <v>162</v>
+      </c>
+      <c r="B164" t="s">
+        <v>136</v>
+      </c>
+      <c r="C164" t="s">
+        <v>162</v>
+      </c>
+      <c r="D164" t="s">
+        <v>143</v>
+      </c>
+      <c r="E164" t="s">
+        <v>169</v>
+      </c>
+      <c r="F164">
+        <v>0.2095</v>
+      </c>
+      <c r="G164">
+        <v>0.0003</v>
+      </c>
+      <c r="H164">
+        <v>0.0008</v>
+      </c>
+      <c r="I164">
+        <v>0.0302</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9">
+      <c r="A165">
+        <v>163</v>
+      </c>
+      <c r="B165" t="s">
+        <v>136</v>
+      </c>
+      <c r="C165" t="s">
+        <v>162</v>
+      </c>
+      <c r="D165" t="s">
+        <v>144</v>
+      </c>
+      <c r="E165" t="s">
+        <v>170</v>
+      </c>
+      <c r="F165">
+        <v>0.0747</v>
+      </c>
+      <c r="G165">
+        <v>0.1972</v>
+      </c>
+      <c r="H165">
+        <v>0.2333</v>
+      </c>
+      <c r="I165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9">
+      <c r="A166">
+        <v>164</v>
+      </c>
+      <c r="B166" t="s">
+        <v>136</v>
+      </c>
+      <c r="C166" t="s">
+        <v>162</v>
+      </c>
+      <c r="D166" t="s">
+        <v>145</v>
+      </c>
+      <c r="E166" t="s">
+        <v>171</v>
+      </c>
+      <c r="F166">
+        <v>0.2381</v>
+      </c>
+      <c r="G166">
+        <v>0</v>
+      </c>
+      <c r="H166">
+        <v>0.0001</v>
+      </c>
+      <c r="I166">
+        <v>0.0042</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9">
+      <c r="A167">
+        <v>165</v>
+      </c>
+      <c r="B167" t="s">
+        <v>136</v>
+      </c>
+      <c r="C167" t="s">
+        <v>162</v>
+      </c>
+      <c r="D167" t="s">
+        <v>146</v>
+      </c>
+      <c r="E167" t="s">
+        <v>172</v>
+      </c>
+      <c r="F167">
+        <v>0.06660000000000001</v>
+      </c>
+      <c r="G167">
+        <v>0.25</v>
+      </c>
+      <c r="H167">
+        <v>0.2819</v>
+      </c>
+      <c r="I167">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9">
+      <c r="A168">
+        <v>166</v>
+      </c>
+      <c r="B168" t="s">
+        <v>136</v>
+      </c>
+      <c r="C168" t="s">
+        <v>162</v>
+      </c>
+      <c r="D168" t="s">
+        <v>147</v>
+      </c>
+      <c r="E168" t="s">
+        <v>173</v>
+      </c>
+      <c r="F168">
+        <v>0.0645</v>
+      </c>
+      <c r="G168">
+        <v>0.2655</v>
+      </c>
+      <c r="H168">
+        <v>0.2954</v>
+      </c>
+      <c r="I168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9">
+      <c r="A169">
+        <v>167</v>
+      </c>
+      <c r="B169" t="s">
+        <v>136</v>
+      </c>
+      <c r="C169" t="s">
+        <v>162</v>
+      </c>
+      <c r="D169" t="s">
+        <v>148</v>
+      </c>
+      <c r="E169" t="s">
+        <v>174</v>
+      </c>
+      <c r="F169">
+        <v>0.0818</v>
+      </c>
+      <c r="G169">
+        <v>0.1574</v>
+      </c>
+      <c r="H169">
+        <v>0.193</v>
+      </c>
+      <c r="I169">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G11"/>
@@ -26605,13 +31529,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C2" t="s">
         <v>206</v>
-      </c>
-      <c r="C2" t="s">
-        <v>205</v>
       </c>
       <c r="D2">
         <v>0.607</v>
@@ -26619,16 +31543,16 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D3">
-        <v>0.419</v>
+        <v>0.415</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -26639,38 +31563,38 @@
         <v>204</v>
       </c>
       <c r="C4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D4">
-        <v>0.669</v>
+        <v>0.419</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D5">
-        <v>0.415</v>
+        <v>0.669</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
+        <v>204</v>
+      </c>
+      <c r="C6" t="s">
         <v>207</v>
       </c>
-      <c r="C6" t="s">
-        <v>206</v>
-      </c>
       <c r="D6">
-        <v>0.63</v>
+        <v>0.473</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -26681,10 +31605,10 @@
         <v>207</v>
       </c>
       <c r="C7" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D7">
-        <v>0.473</v>
+        <v>0.63</v>
       </c>
     </row>
   </sheetData>

--- a/research/output/tables/all_results.xlsx
+++ b/research/output/tables/all_results.xlsx
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3292" uniqueCount="674">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3300" uniqueCount="675">
   <si>
     <t>Variable</t>
   </si>
@@ -1833,6 +1833,9 @@
   </si>
   <si>
     <t>Indirect</t>
+  </si>
+  <si>
+    <t>b (M -&gt; Y | X)</t>
   </si>
   <si>
     <t>CSS_distress ~ X</t>
@@ -2894,7 +2897,7 @@
         <v>0.048</v>
       </c>
       <c r="I2">
-        <v>0.23</v>
+        <v>0.221</v>
       </c>
       <c r="J2">
         <v>0.166</v>
@@ -2929,7 +2932,7 @@
         <v>0.11</v>
       </c>
       <c r="I3">
-        <v>0.192</v>
+        <v>0.235</v>
       </c>
       <c r="J3">
         <v>0.132</v>
@@ -2999,7 +3002,7 @@
         <v>0.038</v>
       </c>
       <c r="I5">
-        <v>0.132</v>
+        <v>0.192</v>
       </c>
       <c r="J5">
         <v>0.035</v>
@@ -3034,7 +3037,7 @@
         <v>0.096</v>
       </c>
       <c r="I6">
-        <v>0.144</v>
+        <v>0.175</v>
       </c>
       <c r="J6">
         <v>0.063</v>
@@ -3069,7 +3072,7 @@
         <v>0.025</v>
       </c>
       <c r="I7">
-        <v>0.115</v>
+        <v>0.132</v>
       </c>
       <c r="J7">
         <v>0.029</v>
@@ -3104,7 +3107,7 @@
         <v>1</v>
       </c>
       <c r="I8">
-        <v>0.094</v>
+        <v>0.062</v>
       </c>
       <c r="J8">
         <v>0.177</v>
@@ -3118,34 +3121,34 @@
         <v>218</v>
       </c>
       <c r="B9">
-        <v>0.23</v>
+        <v>0.221</v>
       </c>
       <c r="C9">
-        <v>0.192</v>
+        <v>0.235</v>
       </c>
       <c r="D9">
         <v>0.221</v>
       </c>
       <c r="E9">
+        <v>0.192</v>
+      </c>
+      <c r="F9">
+        <v>0.175</v>
+      </c>
+      <c r="G9">
         <v>0.132</v>
       </c>
-      <c r="F9">
-        <v>0.144</v>
-      </c>
-      <c r="G9">
-        <v>0.115</v>
-      </c>
       <c r="H9">
-        <v>0.094</v>
+        <v>0.062</v>
       </c>
       <c r="I9">
         <v>1</v>
       </c>
       <c r="J9">
-        <v>0.322</v>
+        <v>0.233</v>
       </c>
       <c r="K9">
-        <v>-0.08500000000000001</v>
+        <v>-0.063</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -3174,7 +3177,7 @@
         <v>0.177</v>
       </c>
       <c r="I10">
-        <v>0.322</v>
+        <v>0.233</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -3209,7 +3212,7 @@
         <v>0.053</v>
       </c>
       <c r="I11">
-        <v>-0.08500000000000001</v>
+        <v>-0.063</v>
       </c>
       <c r="J11">
         <v>-0.08500000000000001</v>
@@ -3286,13 +3289,13 @@
         <v>0.4604</v>
       </c>
       <c r="I2">
-        <v>0.0001</v>
+        <v>0.0003</v>
       </c>
       <c r="J2">
-        <v>0.0074</v>
+        <v>0.0068</v>
       </c>
       <c r="K2">
-        <v>0.002</v>
+        <v>0.0019</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -3321,13 +3324,13 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I3">
-        <v>0.0019</v>
+        <v>0.0001</v>
       </c>
       <c r="J3">
-        <v>0.0373</v>
+        <v>0.0364</v>
       </c>
       <c r="K3">
-        <v>0.2625</v>
+        <v>0.2784</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -3353,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>0.0022</v>
+        <v>0.0021</v>
       </c>
       <c r="I4">
         <v>0.0003</v>
@@ -3391,13 +3394,13 @@
         <v>0.543</v>
       </c>
       <c r="I5">
-        <v>0.0373</v>
+        <v>0.0018</v>
       </c>
       <c r="J5">
         <v>0.5718</v>
       </c>
       <c r="K5">
-        <v>0.1909</v>
+        <v>0.2024</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -3426,10 +3429,10 @@
         <v>0.1469</v>
       </c>
       <c r="I6">
-        <v>0.0223</v>
+        <v>0.0043</v>
       </c>
       <c r="J6">
-        <v>0.3433</v>
+        <v>0.3531</v>
       </c>
       <c r="K6">
         <v>0.543</v>
@@ -3461,7 +3464,7 @@
         <v>0.6685</v>
       </c>
       <c r="I7">
-        <v>0.075</v>
+        <v>0.0364</v>
       </c>
       <c r="J7">
         <v>0.6368</v>
@@ -3481,7 +3484,7 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="D8">
-        <v>0.0022</v>
+        <v>0.0021</v>
       </c>
       <c r="E8">
         <v>0.543</v>
@@ -3496,10 +3499,10 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0.1513</v>
+        <v>0.3555</v>
       </c>
       <c r="J8">
-        <v>0.004</v>
+        <v>0.0038</v>
       </c>
       <c r="K8">
         <v>0.4262</v>
@@ -3510,34 +3513,34 @@
         <v>218</v>
       </c>
       <c r="B9">
+        <v>0.0003</v>
+      </c>
+      <c r="C9">
         <v>0.0001</v>
-      </c>
-      <c r="C9">
-        <v>0.0019</v>
       </c>
       <c r="D9">
         <v>0.0003</v>
       </c>
       <c r="E9">
-        <v>0.0373</v>
+        <v>0.0018</v>
       </c>
       <c r="F9">
-        <v>0.0223</v>
+        <v>0.0043</v>
       </c>
       <c r="G9">
-        <v>0.075</v>
+        <v>0.0364</v>
       </c>
       <c r="H9">
-        <v>0.1513</v>
+        <v>0.3555</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="K9">
-        <v>0.1909</v>
+        <v>0.3531</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -3545,10 +3548,10 @@
         <v>219</v>
       </c>
       <c r="B10">
-        <v>0.0074</v>
+        <v>0.0068</v>
       </c>
       <c r="C10">
-        <v>0.0373</v>
+        <v>0.0364</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -3557,22 +3560,22 @@
         <v>0.5718</v>
       </c>
       <c r="F10">
-        <v>0.3433</v>
+        <v>0.3531</v>
       </c>
       <c r="G10">
         <v>0.6368</v>
       </c>
       <c r="H10">
-        <v>0.004</v>
+        <v>0.0038</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0.1909</v>
+        <v>0.2024</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -3580,16 +3583,16 @@
         <v>220</v>
       </c>
       <c r="B11">
-        <v>0.002</v>
+        <v>0.0019</v>
       </c>
       <c r="C11">
-        <v>0.2625</v>
+        <v>0.2784</v>
       </c>
       <c r="D11">
         <v>0.4435</v>
       </c>
       <c r="E11">
-        <v>0.1909</v>
+        <v>0.2024</v>
       </c>
       <c r="F11">
         <v>0.543</v>
@@ -3601,10 +3604,10 @@
         <v>0.4262</v>
       </c>
       <c r="I11">
-        <v>0.1909</v>
+        <v>0.3531</v>
       </c>
       <c r="J11">
-        <v>0.1909</v>
+        <v>0.2024</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -22879,7 +22882,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -23022,19 +23025,19 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C7" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="D7">
-        <v>0.4621</v>
+        <v>0.3521</v>
       </c>
       <c r="E7">
-        <v>0.361</v>
+        <v>0.2284</v>
       </c>
       <c r="F7">
-        <v>0.5632</v>
+        <v>0.4758</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -23048,16 +23051,16 @@
         <v>587</v>
       </c>
       <c r="C8" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D8">
-        <v>0.3432</v>
+        <v>0.4621</v>
       </c>
       <c r="E8">
-        <v>0.2309</v>
+        <v>0.361</v>
       </c>
       <c r="F8">
-        <v>0.4555</v>
+        <v>0.5632</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -23071,16 +23074,16 @@
         <v>587</v>
       </c>
       <c r="C9" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D9">
-        <v>0.2796</v>
+        <v>0.3432</v>
       </c>
       <c r="E9">
-        <v>0.1659</v>
+        <v>0.2309</v>
       </c>
       <c r="F9">
-        <v>0.3933</v>
+        <v>0.4555</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -23094,19 +23097,19 @@
         <v>587</v>
       </c>
       <c r="C10" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D10">
-        <v>0.1545</v>
+        <v>0.2796</v>
       </c>
       <c r="E10">
-        <v>0.0296</v>
+        <v>0.1659</v>
       </c>
       <c r="F10">
-        <v>0.2794</v>
+        <v>0.3933</v>
       </c>
       <c r="G10">
-        <v>0.0155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -23117,19 +23120,19 @@
         <v>587</v>
       </c>
       <c r="C11" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D11">
-        <v>0.1251</v>
+        <v>0.1545</v>
       </c>
       <c r="E11">
-        <v>0.06619999999999999</v>
+        <v>0.0296</v>
       </c>
       <c r="F11">
-        <v>0.1994</v>
+        <v>0.2794</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>0.0155</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -23137,19 +23140,19 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C12" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D12">
-        <v>0.4618</v>
+        <v>0.1251</v>
       </c>
       <c r="E12">
-        <v>0.3585</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="F12">
-        <v>0.5652</v>
+        <v>0.1994</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -23160,22 +23163,22 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C13" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D13">
-        <v>0.4782</v>
+        <v>0.2706</v>
       </c>
       <c r="E13">
-        <v>0.3762</v>
+        <v>0.1396</v>
       </c>
       <c r="F13">
-        <v>0.5802</v>
+        <v>0.4016</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -23186,19 +23189,19 @@
         <v>588</v>
       </c>
       <c r="C14" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="D14">
-        <v>0.2249</v>
+        <v>0.4618</v>
       </c>
       <c r="E14">
-        <v>0.1108</v>
+        <v>0.3585</v>
       </c>
       <c r="F14">
-        <v>0.3389</v>
+        <v>0.5652</v>
       </c>
       <c r="G14">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -23209,19 +23212,19 @@
         <v>588</v>
       </c>
       <c r="C15" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="D15">
-        <v>0.0051</v>
+        <v>0.4782</v>
       </c>
       <c r="E15">
-        <v>-0.1109</v>
+        <v>0.3762</v>
       </c>
       <c r="F15">
-        <v>0.121</v>
+        <v>0.5802</v>
       </c>
       <c r="G15">
-        <v>0.9316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -23232,19 +23235,19 @@
         <v>588</v>
       </c>
       <c r="C16" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D16">
-        <v>0.2198</v>
+        <v>0.2249</v>
       </c>
       <c r="E16">
-        <v>0.1579</v>
+        <v>0.1108</v>
       </c>
       <c r="F16">
-        <v>0.2928</v>
+        <v>0.3389</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -23252,22 +23255,22 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C17" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D17">
-        <v>0.4925</v>
+        <v>0.0051</v>
       </c>
       <c r="E17">
-        <v>0.39</v>
+        <v>-0.1109</v>
       </c>
       <c r="F17">
-        <v>0.595</v>
+        <v>0.121</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>0.9316</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -23275,19 +23278,19 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C18" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D18">
-        <v>0.4532</v>
+        <v>0.2198</v>
       </c>
       <c r="E18">
-        <v>0.3517</v>
+        <v>0.1579</v>
       </c>
       <c r="F18">
-        <v>0.5546</v>
+        <v>0.2928</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -23298,19 +23301,19 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C19" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D19">
-        <v>0.4694</v>
+        <v>0.4759</v>
       </c>
       <c r="E19">
-        <v>0.3666</v>
+        <v>0.345</v>
       </c>
       <c r="F19">
-        <v>0.5721000000000001</v>
+        <v>0.6068</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -23324,16 +23327,16 @@
         <v>589</v>
       </c>
       <c r="C20" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="D20">
-        <v>0.3215</v>
+        <v>0.4925</v>
       </c>
       <c r="E20">
-        <v>0.2093</v>
+        <v>0.39</v>
       </c>
       <c r="F20">
-        <v>0.4337</v>
+        <v>0.595</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -23347,18 +23350,110 @@
         <v>589</v>
       </c>
       <c r="C21" t="s">
+        <v>597</v>
+      </c>
+      <c r="D21">
+        <v>0.4532</v>
+      </c>
+      <c r="E21">
+        <v>0.3517</v>
+      </c>
+      <c r="F21">
+        <v>0.5546</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>589</v>
+      </c>
+      <c r="C22" t="s">
+        <v>592</v>
+      </c>
+      <c r="D22">
+        <v>0.4694</v>
+      </c>
+      <c r="E22">
+        <v>0.3666</v>
+      </c>
+      <c r="F22">
+        <v>0.5721000000000001</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>589</v>
+      </c>
+      <c r="C23" t="s">
+        <v>593</v>
+      </c>
+      <c r="D23">
+        <v>0.3215</v>
+      </c>
+      <c r="E23">
+        <v>0.2093</v>
+      </c>
+      <c r="F23">
+        <v>0.4337</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>589</v>
+      </c>
+      <c r="C24" t="s">
         <v>594</v>
       </c>
-      <c r="D21">
+      <c r="D24">
         <v>0.1478</v>
       </c>
-      <c r="E21">
+      <c r="E24">
         <v>0.0857</v>
       </c>
-      <c r="F21">
+      <c r="F24">
         <v>0.2186</v>
       </c>
-      <c r="G21">
+      <c r="G24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>589</v>
+      </c>
+      <c r="C25" t="s">
+        <v>595</v>
+      </c>
+      <c r="D25">
+        <v>0.3002</v>
+      </c>
+      <c r="E25">
+        <v>0.1796</v>
+      </c>
+      <c r="F25">
+        <v>0.4207</v>
+      </c>
+      <c r="G25">
         <v>0</v>
       </c>
     </row>
@@ -23391,7 +23486,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C2">
         <v>0.0737</v>
@@ -23408,7 +23503,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C3">
         <v>0.1263</v>
@@ -23425,7 +23520,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C4">
         <v>0.0687</v>
@@ -23442,7 +23537,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C5">
         <v>-0.0438</v>
@@ -23466,10 +23561,10 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="B1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D1" t="s">
         <v>561</v>
@@ -23489,13 +23584,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C2">
         <v>0.1007</v>
       </c>
       <c r="D2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E2">
         <v>0.3431</v>
@@ -23512,13 +23607,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C3">
         <v>-0.1404</v>
       </c>
       <c r="D3" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E3">
         <v>0.4687</v>
@@ -23541,7 +23636,7 @@
         <v>0.0636</v>
       </c>
       <c r="D4" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E4">
         <v>0.6631</v>
@@ -23558,13 +23653,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C5">
         <v>0.0042</v>
       </c>
       <c r="D5" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E5">
         <v>0.9769</v>
@@ -23587,7 +23682,7 @@
         <v>-0.0634</v>
       </c>
       <c r="D6" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E6">
         <v>0.754</v>
@@ -23604,13 +23699,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C7">
         <v>-0.1769</v>
       </c>
       <c r="D7" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E7">
         <v>0.292</v>
@@ -23627,13 +23722,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C8">
         <v>-0.1394</v>
       </c>
       <c r="D8" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E8">
         <v>0.0684</v>
@@ -23968,10 +24063,10 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D1" t="s">
         <v>543</v>
@@ -23988,7 +24083,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C2">
         <v>0.6153</v>
@@ -24008,7 +24103,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C3">
         <v>0.6905</v>
@@ -24028,7 +24123,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C4">
         <v>0.7655999999999999</v>
@@ -24064,13 +24159,13 @@
         <v>32</v>
       </c>
       <c r="E1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="G1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -24081,10 +24176,10 @@
         <v>254</v>
       </c>
       <c r="C2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D2" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E2">
         <v>0.8571</v>
@@ -24104,10 +24199,10 @@
         <v>255</v>
       </c>
       <c r="C3" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D3" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E3">
         <v>0.6538</v>
@@ -24131,13 +24226,13 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E1" t="s">
         <v>214</v>
@@ -24151,10 +24246,10 @@
         <v>254</v>
       </c>
       <c r="C2" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D2" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E2">
         <v>0.0043</v>
@@ -24168,10 +24263,10 @@
         <v>255</v>
       </c>
       <c r="C3" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D3" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E3">
         <v>0.9893</v>
@@ -24182,13 +24277,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C4" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D4" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E4">
         <v>0.6168</v>
@@ -24199,13 +24294,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C5" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D5" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E5">
         <v>0.9154</v>
@@ -24216,13 +24311,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C6" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D6" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E6">
         <v>0.5339</v>
@@ -24233,13 +24328,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C7" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D7" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E7">
         <v>0.6138</v>
@@ -24253,10 +24348,10 @@
         <v>558</v>
       </c>
       <c r="C8" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D8" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E8">
         <v>0.2515</v>
@@ -24274,16 +24369,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="B1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F1" t="s">
         <v>561</v>
@@ -24309,7 +24404,7 @@
         <v>0.4983</v>
       </c>
       <c r="F2" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -24332,7 +24427,7 @@
         <v>0.4502</v>
       </c>
       <c r="F3" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -24355,7 +24450,7 @@
         <v>0.5725</v>
       </c>
       <c r="F4" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -24378,7 +24473,7 @@
         <v>0.3512</v>
       </c>
       <c r="F5" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="G5">
         <v>0.0209</v>
@@ -24401,7 +24496,7 @@
         <v>0.4656</v>
       </c>
       <c r="F6" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="G6">
         <v>0.0011</v>
@@ -24424,7 +24519,7 @@
         <v>0.4851</v>
       </c>
       <c r="F7" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -24447,7 +24542,7 @@
         <v>0.2335</v>
       </c>
       <c r="F8" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="G8">
         <v>0.4022</v>
@@ -24470,7 +24565,7 @@
         <v>0.5508999999999999</v>
       </c>
       <c r="F9" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -24493,7 +24588,7 @@
         <v>0.5004</v>
       </c>
       <c r="F10" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="G10">
         <v>0.0001</v>
@@ -24516,7 +24611,7 @@
         <v>0.3586</v>
       </c>
       <c r="F11" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="G11">
         <v>0.0317</v>
@@ -24539,7 +24634,7 @@
         <v>0.3389</v>
       </c>
       <c r="F12" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="G12">
         <v>0.1329</v>
@@ -24550,7 +24645,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C13" t="s">
         <v>30</v>
@@ -24562,7 +24657,7 @@
         <v>0.4617</v>
       </c>
       <c r="F13" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -24573,7 +24668,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C14" t="s">
         <v>29</v>
@@ -24585,7 +24680,7 @@
         <v>0.4801</v>
       </c>
       <c r="F14" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="G14">
         <v>0.0001</v>
@@ -24608,7 +24703,7 @@
         <v>0.3938</v>
       </c>
       <c r="F15" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -24631,7 +24726,7 @@
         <v>0.4736</v>
       </c>
       <c r="F16" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -24654,7 +24749,7 @@
         <v>0.6066</v>
       </c>
       <c r="F17" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="G17">
         <v>0.0001</v>
@@ -24677,7 +24772,7 @@
         <v>0.5031</v>
       </c>
       <c r="F18" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -24700,7 +24795,7 @@
         <v>0.3976</v>
       </c>
       <c r="F19" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G19">
         <v>0.0001</v>
@@ -24724,7 +24819,7 @@
         <v>117</v>
       </c>
       <c r="D1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E1" t="s">
         <v>74</v>
@@ -25184,16 +25279,16 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F1" t="s">
         <v>222</v>
@@ -25205,7 +25300,7 @@
         <v>223</v>
       </c>
       <c r="I1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="2" spans="1:9">
